--- a/セリフ編集/キャラタイプ別/お嬢様×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×強気.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H300"/>
+  <dimension ref="A1:H333"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1792,7 +1792,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.bold.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.ojousama[1]</t>
+          <t xml:space="preserve">ahead.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1817,14 +1817,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めない……！ この借りは……必ず返す……！</t>
+          <t xml:space="preserve">倒した相手と同じ列に並ばされる屈辱、分かるかしらね？</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.bold.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.ojousama[1]</t>
+          <t xml:space="preserve">behind.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1849,14 +1849,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">虫けらを叩き潰すのは気分がいいわね</t>
+          <t xml:space="preserve">幕を引かれた側の気持ちは、誰も聞きませんのね</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.bold.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.ojousama[1]</t>
+          <t xml:space="preserve">loser.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1881,14 +1881,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">貴方は悪くない相手ですわね。また挑戦して来なさいな</t>
+          <t xml:space="preserve">認めない……！ この借りは……必ず返す……！</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.bold.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.ojousama[1]</t>
+          <t xml:space="preserve">winner.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1913,14 +1913,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この日を待ちわびていたわ。何度も夢で見るくらいに。</t>
+          <t xml:space="preserve">虫けらを叩き潰すのは気分がいいわね</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.bold.ojousama[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.ojousama[1]</t>
+          <t xml:space="preserve">winner.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1945,14 +1945,14 @@
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同感ね。少しは本気にさせてちょうだい…</t>
+          <t xml:space="preserve">貴方は悪くない相手ですわね。また挑戦して来なさいな</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="12">
@@ -1977,14 +1977,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は全力で……つぶしてあげる</t>
+          <t xml:space="preserve">この日を待ちわびていたわ。何度も夢で見るくらいに。</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
@@ -2009,14 +2009,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ええ。相手をしてあげる</t>
+          <t xml:space="preserve">同感ね。少しは本気にさせてちょうだい…</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
@@ -2041,14 +2041,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃がしませんわよ。今日ここで決着をつけましょう？</t>
+          <t xml:space="preserve">今日は全力で……つぶしてあげる</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
@@ -2073,14 +2073,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">飛んで火にいる夏の虫。…と言ったところね</t>
+          <t xml:space="preserve">……ええ。相手をしてあげる</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold.ojousama[1]</t>
+          <t xml:space="preserve">attacker.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2105,14 +2105,14 @@
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の勝利ね。まだ諦めないのかしら？</t>
+          <t xml:space="preserve">逃がしませんわよ。今日ここで決着をつけましょう？</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2122,12 +2122,12 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.ojousama[1]</t>
+          <t xml:space="preserve">defender.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2137,14 +2137,14 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた？…ですが、次がありましてよ！</t>
+          <t xml:space="preserve">飛んで火にいる夏の虫。…と言ったところね</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.ojousama[1]</t>
+          <t xml:space="preserve">winnerLines.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の勝利。…でも、これで折れては居ないのでしょうね</t>
+          <t xml:space="preserve">当然の勝利ね。まだ諦めないのかしら？</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold.ojousama[1]</t>
+          <t xml:space="preserve">loser.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2201,14 +2201,14 @@
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ……！ こんな結果……！</t>
+          <t xml:space="preserve">負けた？…ですが、次がありましてよ！</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.bold.ojousama[1]</t>
+          <t xml:space="preserve">winner.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2233,14 +2233,14 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が{nameA}に宣言した。「もう我慢いたしませんわ！ 全力でお相手して差し上げます！」</t>
+          <t xml:space="preserve">当然の勝利。…でも、これで折れては居ないのでしょうね</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2250,29 +2250,29 @@
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.lose[1]</t>
+          <t xml:space="preserve">loserLines.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。……言い訳はいたしませんわ。</t>
+          <t xml:space="preserve">認めませんわ……！ こんな結果……！</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.lose[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2282,29 +2282,29 @@
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.lose[2]</t>
+          <t xml:space="preserve">awakening.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力及ばずという事ね。</t>
+          <t xml:space="preserve">{nameB}が{nameA}に宣言した。「もう我慢いたしませんわ！ 全力でお相手して差し上げます！」</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.lose[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.lose[3]</t>
+          <t xml:space="preserve">ojousama_bold.lose[1]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2329,14 +2329,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てませんでした。……次は、必ず。</t>
+          <t xml:space="preserve">負けました。……言い訳はいたしませんわ。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.lose[2]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.petition[1]</t>
+          <t xml:space="preserve">ojousama_bold.lose[2]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2361,14 +2361,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あの方はわたくしが引き受けますわね。</t>
+          <t xml:space="preserve">力及ばずという事ね。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.lose[3]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.petition[2]</t>
+          <t xml:space="preserve">ojousama_bold.lose[3]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2393,14 +2393,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方と対戦したいのです。適任はわたくしでしょう。</t>
+          <t xml:space="preserve">勝てませんでした。……次は、必ず。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.petition[1]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.petition[3]</t>
+          <t xml:space="preserve">ojousama_bold.petition[1]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2425,14 +2425,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">名指しさせていただくわ。あの相手との舞台、整えられる?</t>
+          <t xml:space="preserve">社長、あの方はわたくしが引き受けますわね。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.petition[2]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.sendoff[1]</t>
+          <t xml:space="preserve">ojousama_bold.petition[2]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2457,14 +2457,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。期待には応えますわ。</t>
+          <t xml:space="preserve">あの方と対戦したいのです。適任はわたくしでしょう。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.petition[3]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.sendoff[2]</t>
+          <t xml:space="preserve">ojousama_bold.petition[3]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2489,14 +2489,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賢明な判断ね。行ってまいりますわ。</t>
+          <t xml:space="preserve">名指しさせていただくわ。あの相手との舞台、整えられる?</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.sendoff[1]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.sendoff[3]</t>
+          <t xml:space="preserve">ojousama_bold.sendoff[1]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2521,14 +2521,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝しますわ。……結果でお返しするわね。</t>
+          <t xml:space="preserve">ありがとうございます。期待には応えますわ。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.sendoff[2]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.win[1]</t>
+          <t xml:space="preserve">ojousama_bold.sendoff[2]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2553,14 +2553,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったわよ。任せてもらった甲斐はあったでしょう。</t>
+          <t xml:space="preserve">賢明な判断ね。行ってまいりますわ。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.sendoff[3]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.win[2]</t>
+          <t xml:space="preserve">ojousama_bold.sendoff[3]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2585,14 +2585,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">危なげなく、勝ってまいりましたわ。</t>
+          <t xml:space="preserve">感謝しますわ。……結果でお返しするわね。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.win[1]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.win[3]</t>
+          <t xml:space="preserve">ojousama_bold.win[1]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2617,14 +2617,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然勝ちましたわ。機会をいただき、感謝しますわ。</t>
+          <t xml:space="preserve">勝ったわよ。任せてもらった甲斐はあったでしょう。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.win[2]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold._accept[1]</t>
+          <t xml:space="preserve">ojousama_bold.win[2]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2649,14 +2649,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしを選ぶとは、見る目はあるようです。</t>
+          <t xml:space="preserve">危なげなく、勝ってまいりましたわ。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.ojousama_bold.win[3]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold._accept[2]</t>
+          <t xml:space="preserve">ojousama_bold.win[3]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2681,14 +2681,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしい。お受けします。覚悟はおありで?</t>
+          <t xml:space="preserve">当然勝ちましたわ。機会をいただき、感謝しますわ。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold._accept[1]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold._accept[3]</t>
+          <t xml:space="preserve">ojousama_bold._accept[1]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2713,14 +2713,14 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無謀ですけれど……嫌いではありません。</t>
+          <t xml:space="preserve">わたくしを選ぶとは、見る目はあるようです。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold._accept[2]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.draw[1]</t>
+          <t xml:space="preserve">ojousama_bold._accept[2]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2745,14 +2745,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決めさせないとは、生意気なこと。</t>
+          <t xml:space="preserve">よろしい。お受けします。覚悟はおありで?</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold._accept[3]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.draw[2]</t>
+          <t xml:space="preserve">ojousama_bold._accept[3]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2777,14 +2777,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分けなど、わたくしには不本意です。</t>
+          <t xml:space="preserve">無謀ですけれど……嫌いではありません。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.draw[1]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.draw[3]</t>
+          <t xml:space="preserve">ojousama_bold.draw[1]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2809,14 +2809,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わっていません。次で片をつけます。</t>
+          <t xml:space="preserve">決めさせないとは、生意気なこと。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.draw[2]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.lose[1]</t>
+          <t xml:space="preserve">ojousama_bold.draw[2]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……お黙りなさい。今日だけです。</t>
+          <t xml:space="preserve">こうした結末など、わたくしには不本意です。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.draw[3]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.lose[2]</t>
+          <t xml:space="preserve">ojousama_bold.draw[3]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -2873,14 +2873,14 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めます。ただし、今日だけの話です。</t>
+          <t xml:space="preserve">まだ終わっていません。次で片をつけます。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.lose[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.lose[3]</t>
+          <t xml:space="preserve">ojousama_bold.lose[1]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -2905,14 +2905,14 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい。この屈辱は忘れません。</t>
+          <t xml:space="preserve">……お黙りなさい。今日だけです。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.lose[2]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.win[1]</t>
+          <t xml:space="preserve">ojousama_bold.lose[2]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2937,14 +2937,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。この結果に驚きはありません。</t>
+          <t xml:space="preserve">認めます。ただし、今日だけの話です。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.lose[3]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.win[2]</t>
+          <t xml:space="preserve">ojousama_bold.lose[3]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -2969,14 +2969,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身の程は分かりました? …ふふ。</t>
+          <t xml:space="preserve">悔しい。この屈辱は忘れません。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.win[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama_bold.win[3]</t>
+          <t xml:space="preserve">ojousama_bold.win[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3001,14 +3001,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">危なげなく、勝たせていただきました。</t>
+          <t xml:space="preserve">勝ちました。この結果に驚きはありません。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.win[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3018,29 +3018,29 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama_bold.win[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと相応しい舞台が呼んでおりますの。ごきげんよう</t>
+          <t xml:space="preserve">身の程は分かりました? …ふふ。</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.ojousama_bold.win[3]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3050,29 +3050,29 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama_bold.win[3]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仕方ありませんわね、そこまで仰るなら残って差し上げます</t>
+          <t xml:space="preserve">危なげなく、勝たせていただきました。</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.bold.ojousama[1]</t>
+          <t xml:space="preserve">accepted.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3097,14 +3097,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お引き留めには感謝しますが、わたくしの心は決まっておりますの</t>
+          <t xml:space="preserve">もっと相応しい舞台が呼んでおりますの。ごきげんよう</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.bold.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.bold.ojousama[1]</t>
+          <t xml:space="preserve">defended.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3129,14 +3129,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わりでは無いわ</t>
+          <t xml:space="preserve">仕方ありませんわね、そこまで仰るなら残って差し上げます</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.bold.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.bold.ojousama[1]</t>
+          <t xml:space="preserve">defense_failed.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3161,14 +3161,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一シーズン。必ず結果を出しますわ</t>
+          <t xml:space="preserve">お引き留めには感謝しますが、わたくしの心は決まっておりますの</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">default.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3193,14 +3193,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで引き留めるのね。…まぁ、悪くない判断ね</t>
+          <t xml:space="preserve">まだ終わりでは無いわ</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.bold.ojousama[1]</t>
+          <t xml:space="preserve">former_champ.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そこまで言うのなら…もう少しだけ付き合ってあげる</t>
+          <t xml:space="preserve">もう一シーズン。必ず結果を出しますわ</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.bold.ojousama[1]</t>
+          <t xml:space="preserve">heel.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3257,14 +3257,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後に…もう一度、私にふさわしい舞台を用意なさい</t>
+          <t xml:space="preserve">ここで引き留めるのね。…まぁ、悪くない判断ね</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">high_trust.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3289,14 +3289,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくてよ。最後くらい大人しくいたしますわ</t>
+          <t xml:space="preserve">そこまで言うのなら…もう少しだけ付き合ってあげる</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.bold.ojousama[1]</t>
+          <t xml:space="preserve">accept_former_champ.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3321,14 +3321,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんな終わり方ですの。…承知しましたわ</t>
+          <t xml:space="preserve">最後に…もう一度、私にふさわしい舞台を用意なさい</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.bold.ojousama[1]</t>
+          <t xml:space="preserve">accept_heel.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3353,14 +3353,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めますわ。もう体が限界だもの</t>
+          <t xml:space="preserve">…よろしくてよ。最後くらい大人しくいたしますわ</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.bold.ojousama[1]</t>
+          <t xml:space="preserve">accept_no_title.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3385,14 +3385,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めたくありませんけれど…結果が全てですわ</t>
+          <t xml:space="preserve">…こんな終わり方ですの。…承知しましたわ</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.bold.ojousama[1]</t>
+          <t xml:space="preserve">accept_terminal.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3417,14 +3417,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">女王である私を引退させようなんて、100年早くてよ</t>
+          <t xml:space="preserve">…認めますわ。もう体が限界だもの</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.bold.ojousama[1]</t>
+          <t xml:space="preserve">accept_winless.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3449,14 +3449,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしが邪魔ですの？ はっきりおっしゃいなさい</t>
+          <t xml:space="preserve">…認めたくありませんけれど…結果が全てですわ</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.bold.ojousama[1]</t>
+          <t xml:space="preserve">refuse_champ.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3481,14 +3481,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を見限るには早すぎるという事……。良く見ていなさいね</t>
+          <t xml:space="preserve">女王である私を引退させようなんて、100年早くてよ</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">refuse_distrust.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3513,14 +3513,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしがいなくなったら、この団体は終わりですわよ？</t>
+          <t xml:space="preserve">わたくしが邪魔ですの？ はっきりおっしゃいなさい</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">refuse_fighting.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3545,14 +3545,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの時代でしたわ。異論はございませんわね</t>
+          <t xml:space="preserve">私を見限るには早すぎるという事……。良く見ていなさいね</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.bold.ojousama[1]</t>
+          <t xml:space="preserve">refuse_heel.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私ほどの者が王座を得られないなんて…不甲斐ないわね</t>
+          <t xml:space="preserve">わたくしがいなくなったら、この団体は終わりですわよ？</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">A1_champion.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3609,14 +3609,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お泣きにならないで。みっともなくてよ</t>
+          <t xml:space="preserve">わたくしの時代でしたわ。異論はございませんわね</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.bold.ojousama[1]</t>
+          <t xml:space="preserve">A2_uncrowned.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3641,14 +3641,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">長いようで…あっという間でしたわね</t>
+          <t xml:space="preserve">私ほどの者が王座を得られないなんて…不甲斐ないわね</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.bold.ojousama[1]</t>
+          <t xml:space="preserve">A3_heel.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3673,14 +3673,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この私が……こんな所で終わりなの？</t>
+          <t xml:space="preserve">お泣きにならないで。みっともなくてよ</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.bold.ojousama[1]</t>
+          <t xml:space="preserve">A4_veteran.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3705,14 +3705,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだやれると信じていましたのに…！</t>
+          <t xml:space="preserve">長いようで…あっという間でしたわね</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.bold.ojousama[1]</t>
+          <t xml:space="preserve">B1_young.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3737,14 +3737,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気持ちは以前のままだけれど、身体はいう事を聞かないみたい…潮時ね</t>
+          <t xml:space="preserve">この私が……こんな所で終わりなの？</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.bold.ojousama[1]</t>
+          <t xml:space="preserve">B2_prime.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3769,14 +3769,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">女王のままに引退……有終の美といったところね。</t>
+          <t xml:space="preserve">まだやれると信じていましたのに…！</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">B3_older.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3801,14 +3801,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こちらに残りますわ。頂点は、わたくしのものなのだから。</t>
+          <t xml:space="preserve">気持ちは以前のままだけれど、身体はいう事を聞かないみたい…潮時ね</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3818,29 +3818,29 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.bold.ojousama[1]</t>
+          <t xml:space="preserve">B4_champion_injury.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……理解が早いわね。この評価に見合う結果を期待していなさい。</t>
+          <t xml:space="preserve">女王のままに引退……有終の美といったところね。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.bold.ojousama[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3850,29 +3850,29 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今はこういう評価という事ね。次はきちんとした評価を期待しますわ。</t>
+          <t xml:space="preserve">こちらに残りますわ。頂点は、わたくしのものなのだから。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.bold.ojousama[1]</t>
+          <t xml:space="preserve">raise_accept.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3897,14 +3897,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……左様ですか。ですが社長、次はありませんわよ。</t>
+          <t xml:space="preserve">……理解が早いわね。この評価に見合う結果を期待していなさい。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.bold.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3929,14 +3929,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}申し上げにくいのですが、この待遇はわたくしに見合いませんわ。{record}</t>
+          <t xml:space="preserve">……今はこういう評価という事ね。次はきちんとした評価を期待しますわ。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.bold.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………。そうですか。わたくしにも限度というものがありますのよ？</t>
+          <t xml:space="preserve">……左様ですか。ですが社長、次はありませんわよ。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.bold.ojousama[1]</t>
+          <t xml:space="preserve">raise_open.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -3993,14 +3993,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……聞いてくださるの。{record}わたくし、もっと上の舞台を求めておりますの。</t>
+          <t xml:space="preserve">社長。{tenure}申し上げにくいのですが、この待遇はわたくしに見合いませんわ。{record}</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.bold.ojousama[1]</t>
+          <t xml:space="preserve">raise_refuse.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}決心がつきましたの。わたくし、この団体を去りますわ。</t>
+          <t xml:space="preserve">…………。そうですか。わたくしにも限度というものがありますのよ？</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.bold.ojousama[1]</t>
+          <t xml:space="preserve">sudden_departure.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4057,14 +4057,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふふ。予想通りですわ。{rivalry}ごきげんよう、社長。</t>
+          <t xml:space="preserve">社長、もう無理ですわ。お世話になりました……と申し上げたいところですけれど、正直そうも思えませんの。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.bold.ojousama[1]</t>
+          <t xml:space="preserve">sudden_departure.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今更。　……もう心は決まっているわ</t>
+          <t xml:space="preserve">もう決めました。これ以上ここに留まる理由がありません。ごきげんよう。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.bold.ojousama[1]</t>
+          <t xml:space="preserve">transfer_listen.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4121,274 +4121,274 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……仕方ありませんわね。……あと少しだけ付き合ってあげる。</t>
+          <t xml:space="preserve">……聞いてくださるの。{record}わたくし、もっと上の舞台を求めておりますの。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}決心がつきましたの。わたくし、この団体を去りますわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ふふ。予想通りですわ。{rivalry}ごきげんよう、社長。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……今更。　……もう心は決まっているわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……仕方ありませんわね。……あと少しだけ付き合ってあげる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.bold.ojousama[1]</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr" s="2">
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr" s="12">
+      <c r="D125" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.bold.ojousama[1]</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr" s="2">
+      <c r="E125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr" s="3">
+      <c r="F125" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">わたくしへの評価は光栄だけれど、
 今の団体を裏切るなどあり得ませんわ</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="40" customHeight="1">
-      <c r="A122" t="inlineStr" s="15">
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.bold.ojousama[1]</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr" s="2">
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr" s="12">
+      <c r="D126" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.bold.ojousama[1]</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr" s="2">
+      <c r="E126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr" s="3">
+      <c r="F126" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ここがわたくしの居場所なの。
 出直していらして</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="40" customHeight="1">
-      <c r="A123" t="inlineStr" s="15">
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.bold.ojousama[1]</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr" s="12">
+      <c r="D127" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.bold.ojousama[1]</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr" s="2">
+      <c r="E127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr" s="3">
+      <c r="F127" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">わたくしを引き抜こうと？
 たいした度胸ですわね</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.bold.ojousama[1]</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr" s="12">
+      <c r="D128" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.bold.ojousama[1]</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr" s="2">
+      <c r="E128" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr" s="3">
+      <c r="F128" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">認めてさしあげますわ。
 格の違いをお見せ致します</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ねぇ社長、わたくしどものこと、もっと大切に扱ってくださいませ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ねぇ社長、次のメイン、わたくしたちにお任せいただけませんこと?</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ねぇ社長、わたくしどもの給与、改めてお考えいただけませんこと?</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ねぇ社長、わたくしどもの貢献、きちんと評価していただいておりますの?</t>
-        </is>
-      </c>
-    </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4413,14 +4413,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ社長、ありがとうございますわ。その一言で十分ですの。</t>
+          <t xml:space="preserve">ねぇ社長、わたくしどものこと、もっと大切に扱ってくださいませ。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4445,14 +4445,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの。失礼いたしましたわ。</t>
+          <t xml:space="preserve">ねぇ社長、次のメイン、わたくしたちにお任せいただけませんこと?</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4477,14 +4477,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そういうお心遣いですのね。ありがたく頂戴いたしますわ。</t>
+          <t xml:space="preserve">ねぇ社長、わたくしどもの給与、改めてお考えいただけませんこと?</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4509,14 +4509,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、社長ありがとうございますわ。期待に応えてみせますわよ。</t>
+          <t xml:space="preserve">ねぇ社長、わたくしどもの貢献、きちんと評価していただいておりますの?</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4541,14 +4541,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの。わかりましたわ。</t>
+          <t xml:space="preserve">まあ社長、ありがとうございますわ。その一言で十分ですの。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4573,14 +4573,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そういうご配慮ですのね。ありがたく頂戴いたしますわ。</t>
+          <t xml:space="preserve">…そうですの。失礼いたしましたわ。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4605,14 +4605,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ社長、ありがとうございますわ。みんなに伝えますわね。</t>
+          <t xml:space="preserve">…まあ、そういうお心遣いですのね。ありがたく頂戴いたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4637,14 +4637,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの。承知いたしましたわ。</t>
+          <t xml:space="preserve">まあ、社長ありがとうございますわ。期待に応えてみせますわよ。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4669,14 +4669,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そういうお心遣いですのね。ありがたく頂戴いたしますわ。</t>
+          <t xml:space="preserve">…そうですの。わかりましたわ。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4701,14 +4701,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ社長、ありがとうございますわ。励みになりますの。</t>
+          <t xml:space="preserve">…まあ、そういうご配慮ですのね。ありがたく頂戴いたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4733,14 +4733,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの。失礼いたしましたわ。</t>
+          <t xml:space="preserve">まあ社長、ありがとうございますわ。みんなに伝えますわね。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4765,14 +4765,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そういうお心遣いですのね。ありがたく頂戴いたしますわ。</t>
+          <t xml:space="preserve">…そうですの。承知いたしましたわ。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4797,14 +4797,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの、次はお声をかけますわ。</t>
+          <t xml:space="preserve">…まあ、そういうお心遣いですのね。ありがたく頂戴いたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4829,14 +4829,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。仲間内のお付き合いも大事ですものね。</t>
+          <t xml:space="preserve">まあ社長、ありがとうございますわ。励みになりますの。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4861,14 +4861,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの、気をつけますわ。</t>
+          <t xml:space="preserve">…そうですの。失礼いたしましたわ。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4893,14 +4893,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。</t>
+          <t xml:space="preserve">…まあ、そういうお心遣いですのね。ありがたく頂戴いたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4925,14 +4925,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの、営業に響くなら線を引きますわ。</t>
+          <t xml:space="preserve">…そうですの、次はお声をかけますわ。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4957,14 +4957,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。これも仕事のうちですもの。</t>
+          <t xml:space="preserve">…ありがとうございますわ。仲間内のお付き合いも大事ですものね。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -4989,14 +4989,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご迷惑おかけしましたわ。明日から、ちゃんと出ますわ。</t>
+          <t xml:space="preserve">…そうですの、気をつけますわ。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5021,14 +5021,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。次はちゃんといたしますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5053,14 +5053,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そういうご配慮ですのね。ありがたく頂戴いたしますわ。</t>
+          <t xml:space="preserve">…そうですの、営業に響くなら線を引きますわ。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5085,14 +5085,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。少し休ませていただきますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。これも仕事のうちですもの。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5117,14 +5117,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫ですわ。問題ございませんわ。</t>
+          <t xml:space="preserve">…ご迷惑おかけしましたわ。明日から、ちゃんと出ますわ。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5149,14 +5149,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、メンバーケアですの。わたくしも楽になりますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。次はちゃんといたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5181,14 +5181,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの。わたくしから皆に話しますわ。</t>
+          <t xml:space="preserve">…まあ、そういうご配慮ですのね。ありがたく頂戴いたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5213,14 +5213,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。穏便にいたしますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。少し休ませていただきますわ。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5245,14 +5245,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、ご配慮ありがたく頂戴いたしますわ。下の子のフォロー、助かりますわ。</t>
+          <t xml:space="preserve">…大丈夫ですわ。問題ございませんわ。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5277,14 +5277,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの。気をつけますわ。</t>
+          <t xml:space="preserve">…まあ、メンバーケアですの。わたくしも楽になりますわ。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5309,14 +5309,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（扇を畳むように、口を閉ざしましたわ）</t>
+          <t xml:space="preserve">…そうですの。わたくしから皆に話しますわ。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5341,14 +5341,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、ご配慮ありがたく頂戴いたしますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。穏便にいたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知いたしましたわ。怪我は本末転倒ですものね、緩めますわ。</t>
+          <t xml:space="preserve">…まあ、ご配慮ありがたく頂戴いたしますわ。下の子のフォロー、助かりますわ。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5405,14 +5405,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。このまま続けますわ。</t>
+          <t xml:space="preserve">…そうですの。気をつけますわ。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5437,14 +5437,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、下の子のケアですのね。ありがたく頂戴いたしますわ。</t>
+          <t xml:space="preserve">（扇を畳むように、口を閉ざしましたわ）</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.ojousama</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.attack.ojousama</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5469,14 +5469,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう、同じ場所には立てませんわ</t>
+          <t xml:space="preserve">…まあ、ご配慮ありがたく頂戴いたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.ojousama</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5486,12 +5486,12 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.defend.ojousama</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5501,29 +5501,29 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等ですわ。お受けいたしましょう</t>
+          <t xml:space="preserve">…承知いたしましたわ。怪我は本末転倒ですものね、緩めますわ。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5533,14 +5533,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">筋を通して、あちらへ参りますわ。悪しからず。</t>
+          <t xml:space="preserve">…ありがとうございますわ。このまま続けますわ。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然ね。まだまだこんなものでは無くてよ</t>
+          <t xml:space="preserve">…まあ、下の子のケアですのね。ありがたく頂戴いたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.ojousama</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5582,29 +5582,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.attack.ojousama</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少しでなにかが掴めそうな。……あと一歩ね。</t>
+          <t xml:space="preserve">もう、同じ場所には立てませんわ</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.bold.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.ojousama</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5614,61 +5614,61 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.defend.ojousama</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この壁だけは…超えられないのかしら</t>
+          <t xml:space="preserve">上等ですわ。お受けいたしましょう</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.bold.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂が見えてきましたわ。手を伸ばせば届く距離に</t>
+          <t xml:space="preserve">筋を通して、あちらへ参りますわ。悪しからず。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.bold.ojousama[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5693,14 +5693,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここからが本番ですわ。見ていてくださいませ</t>
+          <t xml:space="preserve">当然ね。まだまだこんなものでは無くてよ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.bold.ojousama[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5725,14 +5725,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂の景色…悪くありませんわね</t>
+          <t xml:space="preserve">もう少しでなにかが掴めそうな。……あと一歩ね。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.bold.ojousama[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5742,12 +5742,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.bold.ojousama[1]</t>
+          <t xml:space="preserve">fresh.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5757,14 +5757,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この声援に恥じぬ試合をお見せしますわ</t>
+          <t xml:space="preserve">今日は調子がいいの。手加減は無用ですわね</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">heavy.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5789,14 +5789,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…燃えないわね。…何をしても、火がつかないのよ</t>
+          <t xml:space="preserve">体は重いですけれど。…認めるつもりはありません</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">warm.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5821,14 +5821,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目が覚めたわ。ここで終わるわけにはかないもの</t>
+          <t xml:space="preserve">まだ動けます。…少し、体が言うことを聞きませんが</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">cap_reached.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5853,14 +5853,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し待たせたかしら？ここからよ</t>
+          <t xml:space="preserve">この壁だけは…超えられないのかしら</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.bold.ojousama[1]</t>
+          <t xml:space="preserve">ovr_elite.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5885,14 +5885,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何をしてるの？私ほどの者が……</t>
+          <t xml:space="preserve">頂が見えてきましたわ。手を伸ばせば届く距離に</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.bold.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.bold.ojousama[1]</t>
+          <t xml:space="preserve">ovr_growth.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう治ったのに…なぜこんなにもたつくの？</t>
+          <t xml:space="preserve">ここからが本番ですわ。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.bold.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.bold.ojousama[1]</t>
+          <t xml:space="preserve">ovr_legend.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5949,14 +5949,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしが…怯える？ そんなはずは</t>
+          <t xml:space="preserve">頂の景色…悪くありませんわね</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.bold.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.bold.ojousama[1]</t>
+          <t xml:space="preserve">pop_star.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5981,14 +5981,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は万全ですのに…気持ちがついてきませんわね</t>
+          <t xml:space="preserve">この声援に恥じぬ試合をお見せしますわ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.bold.ojousama[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5998,29 +5998,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方と全力で戦えたことは、大変名誉ですわ</t>
+          <t xml:space="preserve">…燃えないわね。…何をしても、火がつかないのよ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6030,29 +6030,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この王座はわたくしに最もふさわしい。それを証明し続けますわ</t>
+          <t xml:space="preserve">目が覚めたわ。ここで終わるわけにはかないもの</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6062,29 +6062,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの名が歴史に刻まれる。…ふさわしいと、自分で思えますわ</t>
+          <t xml:space="preserve">少し待たせたかしら？ここからよ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.bold.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6094,29 +6094,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.bold.ojousama[1]</t>
+          <t xml:space="preserve">defeat.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしが最も輝いた一年でしたわね。異論のある方はリングでお待ちしています</t>
+          <t xml:space="preserve">…何をしてるの？私ほどの者が……</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.bold.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6126,29 +6126,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.bold.ojousama[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ですわね。わたくしの実力を見れば、誰もが納得するでしょう？</t>
+          <t xml:space="preserve">もう治ったのに…なぜこんなにもたつくの？</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6158,29 +6158,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームですわよ!! 思い切り暴れますわ!</t>
+          <t xml:space="preserve">わたくしが…怯える？ そんなはずは</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6190,29 +6190,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">penalty_end.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほほほ、わたくしの本気、ご覧に入れましょう!</t>
+          <t xml:space="preserve">体は万全ですのに…気持ちがついてきませんわね</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.ojousama[3]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[3]</t>
+          <t xml:space="preserve">bestMatch.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6237,14 +6237,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリング、わたくしの独壇場にしてみせますわ!</t>
+          <t xml:space="preserve">あの方と全力で戦えたことは、大変名誉ですわ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">champion.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6269,14 +6269,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員ですって!? 胸が熱くなりますわ!!</t>
+          <t xml:space="preserve">この王座はわたくしに最もふさわしい。それを証明し続けますわ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">hallOfFame.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6301,14 +6301,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様方の歓声、まだ耳に焼き付いておりますの!</t>
+          <t xml:space="preserve">わたくしの名が歴史に刻まれる。…ふさわしいと、自分で思えますわ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.ojousama[3]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[3]</t>
+          <t xml:space="preserve">mvp.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6333,14 +6333,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この勢い、止めてはなりませんわよ!!</t>
+          <t xml:space="preserve">わたくしが最も輝いた一年でしたわね。異論のある方はリングでお待ちしています</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.bold.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6350,29 +6350,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.bold.ojousama[1]</t>
+          <t xml:space="preserve">rookie.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだですわ。もっと上を目指しませんと…</t>
+          <t xml:space="preserve">当然の結果ですわね。わたくしの実力を見れば、誰もが納得するでしょう？</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.bold.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6382,29 +6382,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様のご期待が、わたくしの力になっておりますわ</t>
+          <t xml:space="preserve">ドームですわよ!! 思い切り暴れますわ!</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.bold.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6414,29 +6414,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度、問題ありませんわ</t>
+          <t xml:space="preserve">ほほほ、わたくしの本気、ご覧に入れましょう!</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.bold.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.ojousama[3]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6446,29 +6446,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[3]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この声援を力に、さらに上を目指しますわ</t>
+          <t xml:space="preserve">このリング、わたくしの独壇場にしてみせますわ!</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.bold.ojousama[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6478,29 +6478,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この団体で、わたしの夢は叶えられますの…？</t>
+          <t xml:space="preserve">満員ですって!? 胸が熱くなりますわ!!</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.bold.ojousama[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6510,29 +6510,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままで本当によろしいのか、と考えてしまいますの</t>
+          <t xml:space="preserve">お客様方の歓声、まだ耳に焼き付いておりますの!</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.bold.ojousama[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.ojousama[3]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6542,29 +6542,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[3]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わたくしの価値、ちゃんと見てくださっているのかしら</t>
+          <t xml:space="preserve">この勢い、止めてはなりませんわよ!!</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.bold.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.bold.ojousama[1]</t>
+          <t xml:space="preserve">N1.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6589,14 +6589,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わたくしにふさわしい舞台がまだ来ないなんて</t>
+          <t xml:space="preserve">まだまだですわ。もっと上を目指しませんと…</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.bold.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6606,29 +6606,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.bold.ojousama[1]</t>
+          <t xml:space="preserve">N2.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お断りしますわ。わたくしの価値は、この程度ではありませんの</t>
+          <t xml:space="preserve">皆様のご期待が、わたくしの力になっておりますわ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.bold.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6638,29 +6638,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.bold.ojousama[1]</t>
+          <t xml:space="preserve">N3.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。結果でお返しするわ</t>
+          <t xml:space="preserve">この程度、問題ありませんわ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.bold.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.bold.ojousama[1]</t>
+          <t xml:space="preserve">N4.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この合宿で一段上へ参りましょう</t>
+          <t xml:space="preserve">この声援を力に、さらに上を目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.bold.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6702,29 +6702,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.bold.ojousama[1]</t>
+          <t xml:space="preserve">N5_low.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが信じているなら、応えてあげないとかしらね？</t>
+          <t xml:space="preserve">…この団体で、わたしの夢は叶えられますの…？</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.bold.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6734,29 +6734,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.bold.ojousama[1]</t>
+          <t xml:space="preserve">N5_warning.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなところで終わりませんわ！</t>
+          <t xml:space="preserve">…このままで本当によろしいのか、と考えてしまいますの</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.bold.ojousama[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6766,29 +6766,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.bold.ojousama[1]</t>
+          <t xml:space="preserve">G1.voice.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">より広い舞台へということね。当然ね。</t>
+          <t xml:space="preserve">…わたくしの価値、ちゃんと見てくださっているのかしら</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.bold.ojousama[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6798,29 +6798,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.bold.ojousama[1]</t>
+          <t xml:space="preserve">G3.voice.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様の頑張りを、誇りに思いますわ</t>
+          <t xml:space="preserve">…わたくしにふさわしい舞台がまだ来ないなんて</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.bold.ojousama[1]</t>
+          <t xml:space="preserve">bonus_insult.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6845,14 +6845,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すこし休んでまいりますわ。ごめんあそばせ。</t>
+          <t xml:space="preserve">お断りしますわ。わたくしの価値は、この程度ではありませんの</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.bold.ojousama[1]</t>
+          <t xml:space="preserve">bonus.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6877,14 +6877,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この機会、決して無駄にはしない</t>
+          <t xml:space="preserve">ありがとうございます。結果でお返しするわ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.bold.ojousama[1]</t>
+          <t xml:space="preserve">camp.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6909,14 +6909,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が出ればお客様も喜ぶでしょうね。楽しみだわ…</t>
+          <t xml:space="preserve">この合宿で一段上へ参りましょう</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.bold.ojousama[1]</t>
+          <t xml:space="preserve">encourage_high_trust.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6941,14 +6941,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…正直に申しますと、良い条件ですわ</t>
+          <t xml:space="preserve">あなたが信じているなら、応えてあげないとかしらね？</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.bold.ojousama[1]</t>
+          <t xml:space="preserve">encourage.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6973,14 +6973,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンの座、いただきに参りましょう</t>
+          <t xml:space="preserve">こんなところで終わりませんわ！</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.bold.ojousama[1]</t>
+          <t xml:space="preserve">faction_decree.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7005,14 +7005,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれとも決着をつけませんとね……</t>
+          <t xml:space="preserve">納得はしておりません。そこだけは、申し上げておきます</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.bold.ojousama[1]</t>
+          <t xml:space="preserve">media.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7037,14 +7037,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…情けないけれど、もう、体が限界ですわね</t>
+          <t xml:space="preserve">より広い舞台へということね。当然ね。</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7054,12 +7054,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.bold.ojousama[1]</t>
+          <t xml:space="preserve">party.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7069,14 +7069,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは納得できませんわね。……どうするか、考えなさいね？</t>
+          <t xml:space="preserve">皆様の頑張りを、誇りに思いますわ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7086,12 +7086,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.bold.ojousama[1]</t>
+          <t xml:space="preserve">refresh_leave.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7101,14 +7101,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと上を目指す為に。特訓が必要ね…</t>
+          <t xml:space="preserve">すこし休んでまいりますわ。ごめんあそばせ。</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.bold.ojousama[1]</t>
+          <t xml:space="preserve">special_treatment.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7133,14 +7133,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">若手の面倒を見るのも、私の務めですわね</t>
+          <t xml:space="preserve">すぐ戻ります。待っていなさいな。</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.bold.ojousama[1]</t>
+          <t xml:space="preserve">trainer.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7165,14 +7165,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなところで止まるわけにはいかないわ…</t>
+          <t xml:space="preserve">この機会、決して無駄にはしない</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.bold.ojousama[1]</t>
+          <t xml:space="preserve">E1.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7197,14 +7197,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの女の態度は許せないわね……</t>
+          <t xml:space="preserve">私が出ればお客様も喜ぶでしょうね。楽しみだわ…</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.bold.ojousama[1]</t>
+          <t xml:space="preserve">E6.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7229,14 +7229,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私も黙ってはいられませんわ。あちらに非があるのだから</t>
+          <t xml:space="preserve">…正直に申しますと、良い条件ですわ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.bold.ojousama[1]</t>
+          <t xml:space="preserve">S_boycott.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7261,14 +7261,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私なら、確かにブランドイメージは上がるでしょうね</t>
+          <t xml:space="preserve">練習…？ 出していただけないのに、意味がありますか</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7278,12 +7278,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.bold.ojousama[1]</t>
+          <t xml:space="preserve">S_boycott.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7293,14 +7293,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM？仕方ないわね……品と格というものを知らしめなければ</t>
+          <t xml:space="preserve">リングに上がれないのなら、稽古など無駄でしょう</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.bold.ojousama[1]</t>
+          <t xml:space="preserve">S_grumble.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7325,14 +7325,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方々に最高の時間をお届けしますわ</t>
+          <t xml:space="preserve">（「なぜわたくしたちがこんな扱いを受けねばならないの」と控室で声を張っている）</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.bold.ojousama[1]</t>
+          <t xml:space="preserve">S_sns.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7357,14 +7357,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイね……もちろん自信はあるわよ？</t>
+          <t xml:space="preserve">（SNSに「このまま終わるつもりはございません」と宣言めいた投稿）</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.bold.ojousama[1]</t>
+          <t xml:space="preserve">S1.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7389,14 +7389,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">撮影？私の魅力を引き出せるのかしら？</t>
+          <t xml:space="preserve">チャンピオンの座、いただきに参りましょう</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7406,12 +7406,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.bold.ojousama[1]</t>
+          <t xml:space="preserve">S2.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7421,14 +7421,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">トーク番組？妙な仕事を持ってくるものね</t>
+          <t xml:space="preserve">あれとも決着をつけませんとね……</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.bold.ojousama[1]</t>
+          <t xml:space="preserve">S3.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7453,14 +7453,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、全国の皆様も私の事が気にかかるのかしら？</t>
+          <t xml:space="preserve">…情けないけれど、もう、体が限界ですわね</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7470,29 +7470,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">S4_direct.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
+          <t xml:space="preserve">このままでは納得できませんわね。……どうするか、考えなさいね？</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7502,29 +7502,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">S4_silent.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">…………（膝の上で、手を固く握りしめている）</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7534,29 +7534,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">S5.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんに立ちますわよ。当然ですの</t>
+          <t xml:space="preserve">もっと上を目指す為に。特訓が必要ね…</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7566,29 +7566,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">S6.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">若手の面倒を見るのも、私の務めですわね</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7598,29 +7598,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">B1.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
+          <t xml:space="preserve">こんなところで止まるわけにはいかないわ…</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7630,29 +7630,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">B2_fighter1.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
+          <t xml:space="preserve">あの女の態度は許せないわね……</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7662,29 +7662,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">B2_fighter2.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を止めるには足りませんわよ</t>
+          <t xml:space="preserve">私も黙ってはいられませんわ。あちらに非があるのだから</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7694,29 +7694,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.bold.ojousama[1]</t>
+          <t xml:space="preserve">B4_brand.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
+          <t xml:space="preserve">私なら、確かにブランドイメージは上がるでしょうね</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7726,29 +7726,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.ojousama[1]</t>
+          <t xml:space="preserve">B4_cm.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">CM？仕方ないわね……品と格というものを知らしめなければ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.ojousama[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7758,29 +7758,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.ojousama[2]</t>
+          <t xml:space="preserve">B4_fan.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんに立ちますわよ。当然ですの</t>
+          <t xml:space="preserve">ファンの方々に最高の時間をお届けしますわ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.bold.ojousama[1]</t>
+          <t xml:space="preserve">B4_fashion.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">ランウェイね……もちろん自信はあるわよ？</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7822,29 +7822,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.bold.ojousama[1]</t>
+          <t xml:space="preserve">B4_gravure.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
+          <t xml:space="preserve">撮影？私の魅力を引き出せるのかしら？</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7854,29 +7854,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.ojousama[1]</t>
+          <t xml:space="preserve">B4_variety.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
+          <t xml:space="preserve">トーク番組？妙な仕事を持ってくるものね</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.ojousama[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7886,29 +7886,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.ojousama[2]</t>
+          <t xml:space="preserve">B4.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を止めるには足りませんわよ</t>
+          <t xml:space="preserve">あらあら、全国の皆様も私の事が気にかかるのかしら？</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7933,14 +7933,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
+          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.ojousama[2]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7965,14 +7965,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで終わりではありませんわよ</t>
+          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7997,14 +7997,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
+          <t xml:space="preserve">てっぺんに立ちますわよ。当然ですの</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8029,14 +8029,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ…！もう一度お願いいたします！</t>
+          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8061,14 +8061,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもお譲りしませんわ。もっと上を目指しますの</t>
+          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8093,14 +8093,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ…！必ず取り返しますの！</t>
+          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8125,14 +8125,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちましたわ。でもここからが本当の闘いですの</t>
+          <t xml:space="preserve">私を止めるには足りませんわよ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8157,14 +8157,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
+          <t xml:space="preserve">倒した相手と同じ列に並ばされる屈辱、分かるかしらね？</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">bitterPrematch.behind.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8189,14 +8189,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで終わりではありませんわよ</t>
+          <t xml:space="preserve">幕を引かれた側の気持ちは、誰も聞きませんのね</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">draftInterest.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8221,14 +8221,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
+          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">draftJoin.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8253,14 +8253,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ…！もう一度お願いいたします！</t>
+          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8270,12 +8270,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">draftJoin.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8285,14 +8285,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもお譲りしませんわ。もっと上を目指しますの</t>
+          <t xml:space="preserve">てっぺんに立ちますわよ。当然ですの</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">faGreeting.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8317,14 +8317,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ…！必ず取り返しますの！</t>
+          <t xml:space="preserve">チャンスをありがとう。私を侮ったあいつらに、ほえ面かかせてやりますわ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">faSigning.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8349,14 +8349,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちましたわ。でもここからが本当の闘いですの</t>
+          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8366,29 +8366,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">faWelcome.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良き仲間になれそうですわ。認めてあげます</t>
+          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8398,29 +8398,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたち、最強のペアですわ</t>
+          <t xml:space="preserve">今日は調子がいいの。手加減は無用ですわね</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8430,29 +8430,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">打ち負かすこと、楽しみにしておりますわ</t>
+          <t xml:space="preserve">体は重いですけれど。…認めるつもりはありません</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8462,29 +8462,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">heatSelf.warm.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">打ち破ることが、わたくしの使命ですわ</t>
+          <t xml:space="preserve">まだ動けます。…少し、体が言うことを聞きませんが</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8494,29 +8494,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.ojousama[1]</t>
+          <t xml:space="preserve">injury.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の看板、わたくしが背負って差し上げますわ</t>
+          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8526,29 +8526,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.ojousama[1]</t>
+          <t xml:space="preserve">injury.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの価値をご理解いただけていませんわね</t>
+          <t xml:space="preserve">私を止めるには足りませんわよ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8558,29 +8558,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.bold.ojousama[1]</t>
+          <t xml:space="preserve">release.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの出番がないとは…運営の怠慢ですわ</t>
+          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8590,29 +8590,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">release.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの感覚は抜けてしまった？でも、得るものは十分でしたわ</t>
+          <t xml:space="preserve">これで終わりではありませんわよ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8622,29 +8622,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.ojousama[1]</t>
+          <t xml:space="preserve">rentalGreeting.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷の一つや二つ、どうということはありませんわ。最後まで、頂は渡しませんの</t>
+          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8654,29 +8654,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.ojousama[2]</t>
+          <t xml:space="preserve">scoutGreeting.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで勝ち残ったのはわたくしですわ。締めくくりも、当然わたくしが</t>
+          <t xml:space="preserve">あら、お目が高いわね。わたくしに気づくなんて</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8686,29 +8686,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.ojousama[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと殊勝なこと。ですが、わたくしを越えるのは無理ですわ</t>
+          <t xml:space="preserve">認めませんわ…！もう一度お願いいたします！</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8718,29 +8718,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.ojousama[2]</t>
+          <t xml:space="preserve">titleDefense.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どなたがお相手でも、このリングの主はわたくしですのよ</t>
+          <t xml:space="preserve">まだ誰にもお譲りしませんわ。もっと上を目指しますの</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8750,29 +8750,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.ojousama[1]</t>
+          <t xml:space="preserve">titleLoss.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、片づけましたわ。…息は乱れていますけれど、まだまだですのよ。次はどなた?</t>
+          <t xml:space="preserve">認めませんわ…！必ず取り返しますの！</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8782,29 +8782,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.ojousama[2]</t>
+          <t xml:space="preserve">titleWin.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリングの主は、まだわたくしですわ。次の方、覚悟していらして</t>
+          <t xml:space="preserve">頂点に立ちましたわ。でもここからが本当の闘いですの</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8814,29 +8814,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この三人が最強でしたわ。他に何か語る必要がありまして？</t>
+          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8846,29 +8846,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.ojousama[2]</t>
+          <t xml:space="preserve">bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたち三人の前に、立てる団体はございませんでしたわね</t>
+          <t xml:space="preserve">これで終わりではありませんわよ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8878,29 +8878,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お賞はいただきますわ。ですが……次は優勝旗もわたくしの手元に参りますのよ</t>
+          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8910,29 +8910,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.ojousama[2]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしを甘く見ないでくださいまし。次は、全てを奪い返しますわ</t>
+          <t xml:space="preserve">認めませんわ…！もう一度お願いいたします！</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8942,29 +8942,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人お相手しようと、わたくしを倒せなかった事実は変わりませんわ</t>
+          <t xml:space="preserve">まだ誰にもお譲りしませんわ。もっと上を目指しますの</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8974,29 +8974,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.ojousama[2]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと……けれど、このリングの主はわたくしでしたのよ</t>
+          <t xml:space="preserve">認めませんわ…！必ず取り返しますの！</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9006,29 +9006,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝はわたくしのもの。当然の結果ですわね</t>
+          <t xml:space="preserve">頂点に立ちましたわ。でもここからが本当の闘いですの</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9038,29 +9038,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.ojousama[2]</t>
+          <t xml:space="preserve">bond_39_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これがわたくしの実力。誰もかれもわかったかしら？</t>
+          <t xml:space="preserve">合いません。どうしても</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9070,29 +9070,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんな結果…ありえないっ…！</t>
+          <t xml:space="preserve">これ以上は望めません。それだけのこと</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9102,29 +9102,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.bold.ojousama[2]</t>
+          <t xml:space="preserve">bond_59_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしともあろうものが…屈辱ですわ</t>
+          <t xml:space="preserve">壁を作られている気がします。愉快ではありませんね</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9134,29 +9134,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ね</t>
+          <t xml:space="preserve">以前はもっと言葉を交わしていたはず。…何なのかしら</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9166,29 +9166,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.bold.ojousama[2]</t>
+          <t xml:space="preserve">bond_60_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度のことで驚いていては、私については来れなくてよ？</t>
+          <t xml:space="preserve">良き仲間になれそうですわ。認めてあげます</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9198,29 +9198,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_80_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私がこの程度で喜ぶとでも？…次こそ頂点を取りますわ</t>
+          <t xml:space="preserve">わたくしたち、最強のペアですわ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9230,29 +9230,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.bold.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしなら、この程度当然よ</t>
+          <t xml:space="preserve">……もう、済んだこと</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9262,29 +9262,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝は当然の舞台。このまま優勝もいただきましょう</t>
+          <t xml:space="preserve">決着はつきました。次へ参ります</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9294,29 +9294,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こいつが最後の獲物ね。覚悟は出来てるかしら</t>
+          <t xml:space="preserve">打ち負かすこと、楽しみにしておりますわ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9326,29 +9326,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝つのは私。それ以外のありえないでしょう？</t>
+          <t xml:space="preserve">打ち破ることが、わたくしの使命ですわ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9358,29 +9358,29 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">格の違いを教えてあげる</t>
+          <t xml:space="preserve">あの方がいたから強くなれました。感謝を…けれど負けません</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9390,29 +9390,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の選出は、当然ね</t>
+          <t xml:space="preserve">この戦いは生涯続きます。望むところ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9422,29 +9422,29 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.bold.ojousama[2]</t>
+          <t xml:space="preserve">trust_above_75.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選ばれた以上、出場いたしますわ</t>
+          <t xml:space="preserve">この団体の看板、わたくしが背負って差し上げますわ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9454,29 +9454,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">容赦は出来ないわ。覚悟する事ね</t>
+          <t xml:space="preserve">ふざけないでいただきたい。価値が分からぬなら、もう付き合いきれません</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9486,29 +9486,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この座は渡せませんわね…… ずっと目指してきましたのよ……！</t>
+          <t xml:space="preserve">この扱いは許せません。しかと覚えておくことです</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9518,29 +9518,29 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そちらの団体のレベル、存じておりますわよ？</t>
+          <t xml:space="preserve">わたくしの価値をご理解いただけていませんわね</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9550,29 +9550,29 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">GL-06.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">格の違いをお教えして差し上げますわ</t>
+          <t xml:space="preserve">わたくしの出番がないとは…運営の怠慢ですわ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
@@ -9592,19 +9592,19 @@
       </c>
       <c r="E291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらまあ。逃げ足が速い…格の違いは理解出来たみたいね</t>
+          <t xml:space="preserve">あの感覚は抜けてしまった？でも、得るものは十分でしたわ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">preFinal.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9629,14 +9629,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ……みっともないだこと。</t>
+          <t xml:space="preserve">傷の一つや二つ、どうということはありませんわ。最後まで、頂は渡しませんの</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9646,12 +9646,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.bold.ojousama[1]</t>
+          <t xml:space="preserve">preFinal.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9661,14 +9661,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘…こんな結果…認めませんわ…！</t>
+          <t xml:space="preserve">ここまで勝ち残ったのはわたくしですわ。締めくくりも、当然わたくしが</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9678,12 +9678,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.bold.ojousama[2]</t>
+          <t xml:space="preserve">preMatch.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9693,14 +9693,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそは…必ず…覚悟なさい！</t>
+          <t xml:space="preserve">次から次へと殊勝なこと。ですが、わたくしを越えるのは無理ですわ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.bold.ojousama[1]</t>
+          <t xml:space="preserve">preMatch.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9725,14 +9725,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ですわ。格の違い、おわかりになりまして？</t>
+          <t xml:space="preserve">どなたがお相手でも、このリングの主はわたくしですのよ</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9742,12 +9742,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.bold.ojousama[2]</t>
+          <t xml:space="preserve">survivor.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9757,14 +9757,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">圧勝ですわね。ふふっ</t>
+          <t xml:space="preserve">一人、片づけましたわ。…息は乱れていますけれど、まだまだですのよ。次はどなた?</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">survivor.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9789,14 +9789,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ね。……私を甘く見るべきじゃなかったわね</t>
+          <t xml:space="preserve">このリングの主は、まだわたくしですわ。次の方、覚悟していらして</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">champion.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9821,14 +9821,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で終わりではなくてよ</t>
+          <t xml:space="preserve">この三人が最強でしたわ。他に何か語る必要がありまして？</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.ojousama[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9838,12 +9838,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[3]</t>
+          <t xml:space="preserve">champion.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9853,44 +9853,1100 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の団体に挑むなど……百年早いですわね</t>
+          <t xml:space="preserve">わたくしたち三人の前に、立てる団体はございませんでしたわね</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お賞はいただきますわ。ですが……次は優勝旗もわたくしの手元に参りますのよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしを甘く見ないでくださいまし。次は、全てを奪い返しますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人お相手しようと、わたくしを倒せなかった事実は変わりませんわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次から次へと……けれど、このリングの主はわたくしでしたのよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">優勝はわたくしのもの。当然の結果ですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">これがわたくしの実力。誰もかれもわかったかしら？</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こ、こんな結果…ありえないっ…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしともあろうものが…屈辱ですわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">当然の結果ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この程度のことで驚いていては、私については来れなくてよ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私がこの程度で喜ぶとでも？…次こそ頂点を取りますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしなら、この程度当然よ</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決勝は当然の舞台。このまま優勝もいただきましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こいつが最後の獲物ね。覚悟は出来てるかしら</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝つのは私。それ以外のありえないでしょう？</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">格の違いを教えてあげる</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私の選出は、当然ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">選ばれた以上、出場いたしますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">容赦は出来ないわ。覚悟する事ね</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この座は渡せませんわね…… ずっと目指してきましたのよ……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">そちらの団体のレベル、存じておりますわよ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">格の違いをお教えして差し上げますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらまあ。逃げ足が速い…格の違いは理解出来たみたいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="40" customHeight="1">
+      <c r="A323" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うふふ……みっともないだこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="40" customHeight="1">
+      <c r="A324" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">嘘…こんな結果…認めませんわ…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="40" customHeight="1">
+      <c r="A325" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次こそは…必ず…覚悟なさい！</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="40" customHeight="1">
+      <c r="A326" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">当然の結果ですわ。格の違い、おわかりになりまして？</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="40" customHeight="1">
+      <c r="A327" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">圧勝ですわね。ふふっ</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="40" customHeight="1">
+      <c r="A328" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">当然の結果ね。……私を甘く見るべきじゃなかったわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="40" customHeight="1">
+      <c r="A329" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この程度で終わりではなくてよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="40" customHeight="1">
+      <c r="A330" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.bold.ojousama[3]</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.ojousama[3]</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私の団体に挑むなど……百年早いですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="40" customHeight="1">
+      <c r="A331" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.bold.ojousama[1]</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr" s="2">
+      <c r="B331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr" s="12">
+      <c r="D331" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.bold.ojousama[1]</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr" s="2">
+      <c r="E331" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr" s="3">
+      <c r="F331" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">これが頂点の景色？…馬鹿ね。まだまだ先はあってよ</t>
         </is>
       </c>
     </row>
+    <row r="332" ht="40" customHeight="1">
+      <c r="A332" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">チャンスをありがとう。私を侮ったあいつらに、ほえ面かかせてやりますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="40" customHeight="1">
+      <c r="A333" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、お目が高いわね。わたくしに気づくなんて</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H300"/>
+  <autoFilter ref="A1:H333"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×強気.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H333"/>
+  <dimension ref="A1:H332"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -320,7 +320,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -335,7 +335,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.ojousama[1]</t>
+          <t xml:space="preserve">atk.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -352,7 +352,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -367,7 +367,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.ojousama[2]</t>
+          <t xml:space="preserve">atk.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -384,7 +384,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.ojousama[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -399,7 +399,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.ojousama[3]</t>
+          <t xml:space="preserve">atk.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -416,7 +416,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.ojousama[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.bold[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -431,7 +431,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.ojousama[4]</t>
+          <t xml:space="preserve">atk.ojousama.bold[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -448,7 +448,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -463,7 +463,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.ojousama[1]</t>
+          <t xml:space="preserve">bigmove.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -480,7 +480,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -495,7 +495,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.ojousama[2]</t>
+          <t xml:space="preserve">bigmove.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -512,7 +512,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.ojousama[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -527,7 +527,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.ojousama[3]</t>
+          <t xml:space="preserve">bigmove.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -544,7 +544,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.bold.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -559,7 +559,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.bold.ojousama[1]</t>
+          <t xml:space="preserve">climax.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -576,7 +576,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.bold.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -591,7 +591,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.bold.ojousama[2]</t>
+          <t xml:space="preserve">climax.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -608,7 +608,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -623,7 +623,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -640,7 +640,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -655,7 +655,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -672,7 +672,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.bold.ojousama[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -687,7 +687,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -704,7 +704,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.bold.ojousama[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -719,7 +719,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.bold.ojousama[1]</t>
+          <t xml:space="preserve">badWinner.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -736,7 +736,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.bold.ojousama[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -751,7 +751,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.bold.ojousama[1]</t>
+          <t xml:space="preserve">goodWinner.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -768,7 +768,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -800,7 +800,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -815,7 +815,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -832,7 +832,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.bold.ojousama[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -847,7 +847,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -864,7 +864,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.bold.ojousama[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -879,7 +879,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.ojousama[2]</t>
+          <t xml:space="preserve">loser.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -896,7 +896,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.bold.ojousama[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -911,7 +911,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -928,7 +928,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.bold.ojousama[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -943,7 +943,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.ojousama[2]</t>
+          <t xml:space="preserve">winner.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -960,7 +960,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.bold.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -975,7 +975,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.bold.ojousama[1]</t>
+          <t xml:space="preserve">competition_won.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -992,7 +992,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.bold.ojousama[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.bold.ojousama[2]</t>
+          <t xml:space="preserve">competition_won.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1024,7 +1024,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.bold.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.bold.ojousama[1]</t>
+          <t xml:space="preserve">direct.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1056,7 +1056,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.bold.ojousama[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.bold.ojousama[2]</t>
+          <t xml:space="preserve">direct.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1088,7 +1088,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.bold.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.bold.ojousama[1]</t>
+          <t xml:space="preserve">fa_signing.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1120,7 +1120,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.bold.ojousama[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.bold.ojousama[2]</t>
+          <t xml:space="preserve">fa_signing.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1152,7 +1152,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.ojousama.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.bold.hit[1]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama.hit[1]</t>
+          <t xml:space="preserve">ojousama.bold.hit[1]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1184,7 +1184,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.ojousama.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.bold.hit[2]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama.hit[2]</t>
+          <t xml:space="preserve">ojousama.bold.hit[2]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1216,7 +1216,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.ojousama.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.bold.win[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama.win[1]</t>
+          <t xml:space="preserve">ojousama.bold.win[1]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1248,7 +1248,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.ojousama.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.bold.win[2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama.win[2]</t>
+          <t xml:space="preserve">ojousama.bold.win[2]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1280,7 +1280,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1312,7 +1312,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1344,7 +1344,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.ojousama[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1376,7 +1376,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1408,7 +1408,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1440,7 +1440,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.ojousama[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1472,7 +1472,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1504,7 +1504,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1536,7 +1536,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.ojousama[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1568,7 +1568,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1600,7 +1600,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1632,7 +1632,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.ojousama[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1664,7 +1664,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1696,7 +1696,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1728,7 +1728,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1760,7 +1760,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1792,7 +1792,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.bold.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.bold.ojousama[1]</t>
+          <t xml:space="preserve">ahead.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1824,7 +1824,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.bold.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.bold.ojousama[1]</t>
+          <t xml:space="preserve">behind.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1856,7 +1856,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.bold.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1888,7 +1888,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.bold.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1920,7 +1920,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.bold.ojousama[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1952,7 +1952,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.ojousama[1]</t>
+          <t xml:space="preserve">attacker.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -1984,7 +1984,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.ojousama[1]</t>
+          <t xml:space="preserve">defender.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2016,7 +2016,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.ojousama[1]</t>
+          <t xml:space="preserve">attacker.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2048,7 +2048,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.ojousama[1]</t>
+          <t xml:space="preserve">defender.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2080,7 +2080,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.ojousama[1]</t>
+          <t xml:space="preserve">attacker.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2112,7 +2112,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.ojousama[1]</t>
+          <t xml:space="preserve">defender.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2144,7 +2144,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold.ojousama[1]</t>
+          <t xml:space="preserve">winnerLines.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2176,7 +2176,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2208,7 +2208,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.bold.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2240,7 +2240,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold.ojousama[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold.ojousama[1]</t>
+          <t xml:space="preserve">loserLines.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2272,7 +2272,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.bold.ojousama[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.bold.ojousama[1]</t>
+          <t xml:space="preserve">awakening.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -3072,7 +3072,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.bold.ojousama[1]</t>
+          <t xml:space="preserve">accepted.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3104,7 +3104,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.bold.ojousama[1]</t>
+          <t xml:space="preserve">defended.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3136,7 +3136,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.bold.ojousama[1]</t>
+          <t xml:space="preserve">defense_failed.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3168,7 +3168,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.bold.ojousama[1]</t>
+          <t xml:space="preserve">default.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3200,7 +3200,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.bold.ojousama[1]</t>
+          <t xml:space="preserve">former_champ.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3232,7 +3232,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">heel.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3264,7 +3264,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.bold.ojousama[1]</t>
+          <t xml:space="preserve">high_trust.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3296,7 +3296,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.bold.ojousama[1]</t>
+          <t xml:space="preserve">accept_former_champ.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3328,7 +3328,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">accept_heel.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3360,7 +3360,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.bold.ojousama[1]</t>
+          <t xml:space="preserve">accept_no_title.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3392,7 +3392,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.bold.ojousama[1]</t>
+          <t xml:space="preserve">accept_terminal.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3424,7 +3424,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.bold.ojousama[1]</t>
+          <t xml:space="preserve">accept_winless.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3456,7 +3456,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.bold.ojousama[1]</t>
+          <t xml:space="preserve">refuse_champ.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3488,7 +3488,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.bold.ojousama[1]</t>
+          <t xml:space="preserve">refuse_distrust.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3520,7 +3520,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.bold.ojousama[1]</t>
+          <t xml:space="preserve">refuse_fighting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3552,7 +3552,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">refuse_heel.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3584,7 +3584,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">A1_champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3616,7 +3616,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.bold.ojousama[1]</t>
+          <t xml:space="preserve">A2_uncrowned.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3648,7 +3648,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.bold.ojousama[1]</t>
+          <t xml:space="preserve">A3_heel.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3680,7 +3680,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.bold.ojousama[1]</t>
+          <t xml:space="preserve">A4_veteran.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3712,7 +3712,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.bold.ojousama[1]</t>
+          <t xml:space="preserve">B1_young.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3744,7 +3744,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.bold.ojousama[1]</t>
+          <t xml:space="preserve">B2_prime.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3776,7 +3776,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.bold.ojousama[1]</t>
+          <t xml:space="preserve">B3_older.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3808,7 +3808,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.bold.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.bold.ojousama[1]</t>
+          <t xml:space="preserve">B4_champion_injury.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3840,7 +3840,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3872,7 +3872,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.bold.ojousama[1]</t>
+          <t xml:space="preserve">raise_accept.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3904,7 +3904,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.bold.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3936,7 +3936,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.bold.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3968,7 +3968,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.bold.ojousama[1]</t>
+          <t xml:space="preserve">raise_open.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4000,7 +4000,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.bold.ojousama[1]</t>
+          <t xml:space="preserve">raise_refuse.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4032,7 +4032,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.bold.ojousama[1]</t>
+          <t xml:space="preserve">sudden_departure.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4064,7 +4064,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.ojousama[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.bold.ojousama[2]</t>
+          <t xml:space="preserve">sudden_departure.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4096,7 +4096,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.bold.ojousama[1]</t>
+          <t xml:space="preserve">transfer_listen.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4128,7 +4128,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.bold.ojousama[1]</t>
+          <t xml:space="preserve">transfer_open.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4160,7 +4160,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.bold.ojousama[1]</t>
+          <t xml:space="preserve">transfer_release.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4192,7 +4192,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.bold.ojousama[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4224,7 +4224,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.bold.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.bold.ojousama[1]</t>
+          <t xml:space="preserve">transfer_retain_success.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4256,7 +4256,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.bold.ojousama[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.bold.ojousama[1]</t>
+          <t xml:space="preserve">blocked.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4289,7 +4289,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.bold.ojousama[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.bold.ojousama[1]</t>
+          <t xml:space="preserve">fail.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4322,7 +4322,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.bold.ojousama[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.bold.ojousama[1]</t>
+          <t xml:space="preserve">start.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4355,7 +4355,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.bold.ojousama[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.bold.ojousama[1]</t>
+          <t xml:space="preserve">success.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -5636,39 +5636,39 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">筋を通して、あちらへ参りますわ。悪しからず。</t>
+          <t xml:space="preserve">当然ね。まだまだこんなものでは無くてよ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5693,14 +5693,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然ね。まだまだこんなものでは無くてよ</t>
+          <t xml:space="preserve">もう少しでなにかが掴めそうな。……あと一歩ね。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">fresh.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5725,14 +5725,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少しでなにかが掴めそうな。……あと一歩ね。</t>
+          <t xml:space="preserve">今日は調子がいいの。手加減は無用ですわね</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.bold.ojousama[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.bold.ojousama[1]</t>
+          <t xml:space="preserve">heavy.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5757,14 +5757,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は調子がいいの。手加減は無用ですわね</t>
+          <t xml:space="preserve">体は重いですけれど。…認めるつもりはありません</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.bold.ojousama[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.bold.ojousama[1]</t>
+          <t xml:space="preserve">warm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5789,14 +5789,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は重いですけれど。…認めるつもりはありません</t>
+          <t xml:space="preserve">まだ動けます。…少し、体が言うことを聞きませんが</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.bold.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.bold.ojousama[1]</t>
+          <t xml:space="preserve">cap_reached.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5821,14 +5821,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ動けます。…少し、体が言うことを聞きませんが</t>
+          <t xml:space="preserve">この壁だけは…超えられないのかしら</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.bold.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.bold.ojousama[1]</t>
+          <t xml:space="preserve">ovr_elite.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5853,14 +5853,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この壁だけは…超えられないのかしら</t>
+          <t xml:space="preserve">頂が見えてきましたわ。手を伸ばせば届く距離に</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.bold.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.bold.ojousama[1]</t>
+          <t xml:space="preserve">ovr_growth.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5885,14 +5885,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂が見えてきましたわ。手を伸ばせば届く距離に</t>
+          <t xml:space="preserve">ここからが本番ですわ。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.bold.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.bold.ojousama[1]</t>
+          <t xml:space="preserve">ovr_legend.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここからが本番ですわ。見ていてくださいませ</t>
+          <t xml:space="preserve">頂の景色…悪くありませんわね</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.bold.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.bold.ojousama[1]</t>
+          <t xml:space="preserve">pop_star.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5949,14 +5949,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂の景色…悪くありませんわね</t>
+          <t xml:space="preserve">この声援に恥じぬ試合をお見せしますわ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.bold.ojousama[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5981,14 +5981,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この声援に恥じぬ試合をお見せしますわ</t>
+          <t xml:space="preserve">…燃えないわね。…何をしても、火がつかないのよ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6013,14 +6013,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…燃えないわね。…何をしても、火がつかないのよ</t>
+          <t xml:space="preserve">目が覚めたわ。ここで終わるわけにはかないもの</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6045,14 +6045,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目が覚めたわ。ここで終わるわけにはかないもの</t>
+          <t xml:space="preserve">少し待たせたかしら？ここからよ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6062,12 +6062,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">defeat.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6077,14 +6077,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し待たせたかしら？ここからよ</t>
+          <t xml:space="preserve">…何をしてるの？私ほどの者が……</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.bold.ojousama[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6109,14 +6109,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何をしてるの？私ほどの者が……</t>
+          <t xml:space="preserve">もう治ったのに…なぜこんなにもたつくの？</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.bold.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.bold.ojousama[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6141,14 +6141,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう治ったのに…なぜこんなにもたつくの？</t>
+          <t xml:space="preserve">わたくしが…怯える？ そんなはずは</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.bold.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.bold.ojousama[1]</t>
+          <t xml:space="preserve">penalty_end.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6173,14 +6173,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしが…怯える？ そんなはずは</t>
+          <t xml:space="preserve">体は万全ですのに…気持ちがついてきませんわね</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.bold.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6190,29 +6190,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.bold.ojousama[1]</t>
+          <t xml:space="preserve">bestMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は万全ですのに…気持ちがついてきませんわね</t>
+          <t xml:space="preserve">あの方と全力で戦えたことは、大変名誉ですわ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.bold.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.bold.ojousama[1]</t>
+          <t xml:space="preserve">champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6237,14 +6237,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方と全力で戦えたことは、大変名誉ですわ</t>
+          <t xml:space="preserve">この王座はわたくしに最もふさわしい。それを証明し続けますわ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">hallOfFame.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6269,14 +6269,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この王座はわたくしに最もふさわしい。それを証明し続けますわ</t>
+          <t xml:space="preserve">わたくしの名が歴史に刻まれる。…ふさわしいと、自分で思えますわ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.bold.ojousama[1]</t>
+          <t xml:space="preserve">mvp.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6301,14 +6301,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの名が歴史に刻まれる。…ふさわしいと、自分で思えますわ</t>
+          <t xml:space="preserve">わたくしが最も輝いた一年でしたわね。異論のある方はリングでお待ちしています</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.bold.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.bold.ojousama[1]</t>
+          <t xml:space="preserve">rookie.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6333,14 +6333,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしが最も輝いた一年でしたわね。異論のある方はリングでお待ちしています</t>
+          <t xml:space="preserve">当然の結果ですわね。わたくしの実力を見れば、誰もが納得するでしょう？</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.bold.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6365,14 +6365,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ですわね。わたくしの実力を見れば、誰もが納得するでしょう？</t>
+          <t xml:space="preserve">ドームですわよ!! 思い切り暴れますわ!</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6397,14 +6397,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームですわよ!! 思い切り暴れますわ!</t>
+          <t xml:space="preserve">ほほほ、わたくしの本気、ご覧に入れましょう!</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6429,14 +6429,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほほほ、わたくしの本気、ご覧に入れましょう!</t>
+          <t xml:space="preserve">このリング、わたくしの独壇場にしてみせますわ!</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.ojousama[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6461,14 +6461,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリング、わたくしの独壇場にしてみせますわ!</t>
+          <t xml:space="preserve">満員ですって!? 胸が熱くなりますわ!!</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6493,14 +6493,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員ですって!? 胸が熱くなりますわ!!</t>
+          <t xml:space="preserve">お客様方の歓声、まだ耳に焼き付いておりますの!</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6525,14 +6525,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様方の歓声、まだ耳に焼き付いておりますの!</t>
+          <t xml:space="preserve">この勢い、止めてはなりませんわよ!!</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.ojousama[3]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6542,29 +6542,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[3]</t>
+          <t xml:space="preserve">N1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この勢い、止めてはなりませんわよ!!</t>
+          <t xml:space="preserve">まだまだですわ。もっと上を目指しませんと…</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.bold.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.bold.ojousama[1]</t>
+          <t xml:space="preserve">N2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6589,14 +6589,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだですわ。もっと上を目指しませんと…</t>
+          <t xml:space="preserve">皆様のご期待が、わたくしの力になっておりますわ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.bold.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.bold.ojousama[1]</t>
+          <t xml:space="preserve">N3.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6621,14 +6621,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様のご期待が、わたくしの力になっておりますわ</t>
+          <t xml:space="preserve">この程度、問題ありませんわ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.bold.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.bold.ojousama[1]</t>
+          <t xml:space="preserve">N4.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6653,14 +6653,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度、問題ありませんわ</t>
+          <t xml:space="preserve">この声援を力に、さらに上を目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.bold.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.bold.ojousama[1]</t>
+          <t xml:space="preserve">N5_low.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6685,14 +6685,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この声援を力に、さらに上を目指しますわ</t>
+          <t xml:space="preserve">…この団体で、わたしの夢は叶えられますの…？</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.bold.ojousama[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.bold.ojousama[1]</t>
+          <t xml:space="preserve">N5_warning.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6717,14 +6717,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この団体で、わたしの夢は叶えられますの…？</t>
+          <t xml:space="preserve">…このままで本当によろしいのか、と考えてしまいますの</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.bold.ojousama[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.bold.ojousama[1]</t>
+          <t xml:space="preserve">G1.voice.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6749,14 +6749,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままで本当によろしいのか、と考えてしまいますの</t>
+          <t xml:space="preserve">…わたくしの価値、ちゃんと見てくださっているのかしら</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.bold.ojousama[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.bold.ojousama[1]</t>
+          <t xml:space="preserve">G3.voice.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6781,14 +6781,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わたくしの価値、ちゃんと見てくださっているのかしら</t>
+          <t xml:space="preserve">…わたくしにふさわしい舞台がまだ来ないなんて</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6798,29 +6798,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.bold.ojousama[1]</t>
+          <t xml:space="preserve">bonus_insult.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わたくしにふさわしい舞台がまだ来ないなんて</t>
+          <t xml:space="preserve">お断りしますわ。わたくしの価値は、この程度ではありませんの</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.bold.ojousama[1]</t>
+          <t xml:space="preserve">bonus.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6845,14 +6845,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お断りしますわ。わたくしの価値は、この程度ではありませんの</t>
+          <t xml:space="preserve">ありがとうございます。結果でお返しするわ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.bold.ojousama[1]</t>
+          <t xml:space="preserve">camp.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6877,14 +6877,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。結果でお返しするわ</t>
+          <t xml:space="preserve">この合宿で一段上へ参りましょう</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.bold.ojousama[1]</t>
+          <t xml:space="preserve">encourage_high_trust.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6909,14 +6909,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この合宿で一段上へ参りましょう</t>
+          <t xml:space="preserve">あなたが信じているなら、応えてあげないとかしらね？</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.bold.ojousama[1]</t>
+          <t xml:space="preserve">encourage.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6941,14 +6941,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが信じているなら、応えてあげないとかしらね？</t>
+          <t xml:space="preserve">こんなところで終わりませんわ！</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.bold.ojousama[1]</t>
+          <t xml:space="preserve">faction_decree.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6973,14 +6973,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなところで終わりませんわ！</t>
+          <t xml:space="preserve">納得はしておりません。そこだけは、申し上げておきます</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.bold.ojousama[1]</t>
+          <t xml:space="preserve">media.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7005,14 +7005,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">納得はしておりません。そこだけは、申し上げておきます</t>
+          <t xml:space="preserve">より広い舞台へということね。当然ね。</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.bold.ojousama[1]</t>
+          <t xml:space="preserve">party.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7037,14 +7037,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">より広い舞台へということね。当然ね。</t>
+          <t xml:space="preserve">皆様の頑張りを、誇りに思いますわ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.bold.ojousama[1]</t>
+          <t xml:space="preserve">refresh_leave.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7069,14 +7069,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様の頑張りを、誇りに思いますわ</t>
+          <t xml:space="preserve">すこし休んでまいりますわ。ごめんあそばせ。</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.bold.ojousama[1]</t>
+          <t xml:space="preserve">special_treatment.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7101,14 +7101,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すこし休んでまいりますわ。ごめんあそばせ。</t>
+          <t xml:space="preserve">すぐ戻ります。待っていなさいな。</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.bold.ojousama[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.bold.ojousama[1]</t>
+          <t xml:space="preserve">trainer.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7133,14 +7133,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐ戻ります。待っていなさいな。</t>
+          <t xml:space="preserve">この機会、決して無駄にはしない</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.bold.ojousama[1]</t>
+          <t xml:space="preserve">E1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7165,14 +7165,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この機会、決して無駄にはしない</t>
+          <t xml:space="preserve">私が出ればお客様も喜ぶでしょうね。楽しみだわ…</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.bold.ojousama[1]</t>
+          <t xml:space="preserve">E6.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7197,14 +7197,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が出ればお客様も喜ぶでしょうね。楽しみだわ…</t>
+          <t xml:space="preserve">…正直に申しますと、良い条件ですわ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.bold.ojousama[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7229,14 +7229,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…正直に申しますと、良い条件ですわ</t>
+          <t xml:space="preserve">練習…？ 出していただけないのに、意味がありますか</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.bold.ojousama[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7261,14 +7261,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習…？ 出していただけないのに、意味がありますか</t>
+          <t xml:space="preserve">リングに上がれないのなら、稽古など無駄でしょう</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold.ojousama[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.bold.ojousama[2]</t>
+          <t xml:space="preserve">S_grumble.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7293,14 +7293,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングに上がれないのなら、稽古など無駄でしょう</t>
+          <t xml:space="preserve">（「なぜわたくしたちがこんな扱いを受けねばならないの」と控室で声を張っている）</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.bold.ojousama[1]</t>
+          <t xml:space="preserve">S_sns.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7325,14 +7325,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「なぜわたくしたちがこんな扱いを受けねばならないの」と控室で声を張っている）</t>
+          <t xml:space="preserve">（SNSに「このまま終わるつもりはございません」と宣言めいた投稿）</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.bold.ojousama[1]</t>
+          <t xml:space="preserve">S1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7357,14 +7357,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「このまま終わるつもりはございません」と宣言めいた投稿）</t>
+          <t xml:space="preserve">チャンピオンの座、いただきに参りましょう</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.bold.ojousama[1]</t>
+          <t xml:space="preserve">S2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7389,14 +7389,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンの座、いただきに参りましょう</t>
+          <t xml:space="preserve">あれとも決着をつけませんとね……</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.bold.ojousama[1]</t>
+          <t xml:space="preserve">S3.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7421,14 +7421,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれとも決着をつけませんとね……</t>
+          <t xml:space="preserve">…情けないけれど、もう、体が限界ですわね</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.bold.ojousama[1]</t>
+          <t xml:space="preserve">S4_direct.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7453,14 +7453,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…情けないけれど、もう、体が限界ですわね</t>
+          <t xml:space="preserve">このままでは納得できませんわね。……どうするか、考えなさいね？</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.bold.ojousama[1]</t>
+          <t xml:space="preserve">S4_silent.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7485,14 +7485,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは納得できませんわね。……どうするか、考えなさいね？</t>
+          <t xml:space="preserve">…………（膝の上で、手を固く握りしめている）</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.bold.ojousama[1]</t>
+          <t xml:space="preserve">S5.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7517,14 +7517,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（膝の上で、手を固く握りしめている）</t>
+          <t xml:space="preserve">もっと上を目指す為に。特訓が必要ね…</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.bold.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.bold.ojousama[1]</t>
+          <t xml:space="preserve">S6.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7549,14 +7549,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと上を目指す為に。特訓が必要ね…</t>
+          <t xml:space="preserve">若手の面倒を見るのも、私の務めですわね</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7566,12 +7566,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.bold.ojousama[1]</t>
+          <t xml:space="preserve">B1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">若手の面倒を見るのも、私の務めですわね</t>
+          <t xml:space="preserve">こんなところで止まるわけにはいかないわ…</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.bold.ojousama[1]</t>
+          <t xml:space="preserve">B2_fighter1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7613,14 +7613,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなところで止まるわけにはいかないわ…</t>
+          <t xml:space="preserve">あの女の態度は許せないわね……</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.bold.ojousama[1]</t>
+          <t xml:space="preserve">B2_fighter2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7645,14 +7645,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの女の態度は許せないわね……</t>
+          <t xml:space="preserve">私も黙ってはいられませんわ。あちらに非があるのだから</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.bold.ojousama[1]</t>
+          <t xml:space="preserve">B4_brand.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7677,14 +7677,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私も黙ってはいられませんわ。あちらに非があるのだから</t>
+          <t xml:space="preserve">私なら、確かにブランドイメージは上がるでしょうね</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.bold.ojousama[1]</t>
+          <t xml:space="preserve">B4_cm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7709,14 +7709,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私なら、確かにブランドイメージは上がるでしょうね</t>
+          <t xml:space="preserve">CM？仕方ないわね……品と格というものを知らしめなければ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.bold.ojousama[1]</t>
+          <t xml:space="preserve">B4_fan.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7741,14 +7741,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM？仕方ないわね……品と格というものを知らしめなければ</t>
+          <t xml:space="preserve">ファンの方々に最高の時間をお届けしますわ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.bold.ojousama[1]</t>
+          <t xml:space="preserve">B4_fashion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7773,14 +7773,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方々に最高の時間をお届けしますわ</t>
+          <t xml:space="preserve">ランウェイね……もちろん自信はあるわよ？</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.bold.ojousama[1]</t>
+          <t xml:space="preserve">B4_gravure.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7805,14 +7805,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイね……もちろん自信はあるわよ？</t>
+          <t xml:space="preserve">撮影？私の魅力を引き出せるのかしら？</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.bold.ojousama[1]</t>
+          <t xml:space="preserve">B4_variety.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7837,14 +7837,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">撮影？私の魅力を引き出せるのかしら？</t>
+          <t xml:space="preserve">トーク番組？妙な仕事を持ってくるものね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.bold.ojousama[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.bold.ojousama[1]</t>
+          <t xml:space="preserve">B4.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7869,14 +7869,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">トーク番組？妙な仕事を持ってくるものね</t>
+          <t xml:space="preserve">あらあら、全国の皆様も私の事が気にかかるのかしら？</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7886,29 +7886,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、全国の皆様も私の事が気にかかるのかしら？</t>
+          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7933,14 +7933,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
+          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7965,14 +7965,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">てっぺんに立ちますわよ。当然ですの</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7997,14 +7997,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんに立ちますわよ。当然ですの</t>
+          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8029,14 +8029,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8061,14 +8061,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
+          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8093,14 +8093,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
+          <t xml:space="preserve">私を止めるには足りませんわよ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8125,14 +8125,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を止めるには足りませんわよ</t>
+          <t xml:space="preserve">倒した相手と同じ列に並ばされる屈辱、分かるかしらね？</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.bold.ojousama[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8157,14 +8157,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">倒した相手と同じ列に並ばされる屈辱、分かるかしらね？</t>
+          <t xml:space="preserve">幕を引かれた側の気持ちは、誰も聞きませんのね</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.bold.ojousama[1]</t>
+          <t xml:space="preserve">draftInterest.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8189,14 +8189,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">幕を引かれた側の気持ちは、誰も聞きませんのね</t>
+          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.bold.ojousama[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8221,14 +8221,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
+          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.ojousama[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8253,14 +8253,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">てっぺんに立ちますわよ。当然ですの</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.ojousama[2]</t>
+          <t xml:space="preserve">faGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8285,14 +8285,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんに立ちますわよ。当然ですの</t>
+          <t xml:space="preserve">チャンスをありがとう。私を侮ったあいつらに、ほえ面かかせてやりますわ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.bold.ojousama[1]</t>
+          <t xml:space="preserve">faSigning.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8317,14 +8317,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンスをありがとう。私を侮ったあいつらに、ほえ面かかせてやりますわ</t>
+          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.bold.ojousama[1]</t>
+          <t xml:space="preserve">faWelcome.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8349,14 +8349,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.bold.ojousama[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8381,14 +8381,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
+          <t xml:space="preserve">今日は調子がいいの。手加減は無用ですわね</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.bold.ojousama[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8413,14 +8413,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は調子がいいの。手加減は無用ですわね</t>
+          <t xml:space="preserve">体は重いですけれど。…認めるつもりはありません</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.bold.ojousama[1]</t>
+          <t xml:space="preserve">heatSelf.warm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8445,14 +8445,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は重いですけれど。…認めるつもりはありません</t>
+          <t xml:space="preserve">まだ動けます。…少し、体が言うことを聞きませんが</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.bold.ojousama[1]</t>
+          <t xml:space="preserve">injury.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8477,14 +8477,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ動けます。…少し、体が言うことを聞きませんが</t>
+          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.ojousama[1]</t>
+          <t xml:space="preserve">injury.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
+          <t xml:space="preserve">私を止めるには足りませんわよ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.ojousama[2]</t>
+          <t xml:space="preserve">release.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8541,14 +8541,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を止めるには足りませんわよ</t>
+          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.ojousama[1]</t>
+          <t xml:space="preserve">release.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8573,14 +8573,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
+          <t xml:space="preserve">これで終わりではありませんわよ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.ojousama[2]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8605,14 +8605,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで終わりではありませんわよ</t>
+          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.bold.ojousama[1]</t>
+          <t xml:space="preserve">scoutGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8637,14 +8637,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
+          <t xml:space="preserve">あら、お目が高いわね。わたくしに気づくなんて</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.bold.ojousama[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8669,14 +8669,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、お目が高いわね。わたくしに気づくなんて</t>
+          <t xml:space="preserve">認めませんわ…！もう一度お願いいたします！</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.bold.ojousama[1]</t>
+          <t xml:space="preserve">titleDefense.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8701,14 +8701,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ…！もう一度お願いいたします！</t>
+          <t xml:space="preserve">まだ誰にもお譲りしませんわ。もっと上を目指しますの</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.bold.ojousama[1]</t>
+          <t xml:space="preserve">titleLoss.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8733,14 +8733,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもお譲りしませんわ。もっと上を目指しますの</t>
+          <t xml:space="preserve">認めませんわ…！必ず取り返しますの！</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.bold.ojousama[1]</t>
+          <t xml:space="preserve">titleWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8765,14 +8765,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ…！必ず取り返しますの！</t>
+          <t xml:space="preserve">頂点に立ちましたわ。でもここからが本当の闘いですの</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8797,14 +8797,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちましたわ。でもここからが本当の闘いですの</t>
+          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8829,14 +8829,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
+          <t xml:space="preserve">これで終わりではありませんわよ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8861,14 +8861,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで終わりではありませんわよ</t>
+          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8893,14 +8893,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
+          <t xml:space="preserve">認めませんわ…！もう一度お願いいたします！</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8910,12 +8910,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8925,14 +8925,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ…！もう一度お願いいたします！</t>
+          <t xml:space="preserve">まだ誰にもお譲りしませんわ。もっと上を目指しますの</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8942,12 +8942,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8957,14 +8957,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもお譲りしませんわ。もっと上を目指しますの</t>
+          <t xml:space="preserve">認めませんわ…！必ず取り返しますの！</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8989,14 +8989,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ…！必ず取り返しますの！</t>
+          <t xml:space="preserve">頂点に立ちましたわ。でもここからが本当の闘いですの</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9006,29 +9006,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちましたわ。でもここからが本当の闘いですの</t>
+          <t xml:space="preserve">合いません。どうしても</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9053,14 +9053,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合いません。どうしても</t>
+          <t xml:space="preserve">これ以上は望めません。それだけのこと</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">bond_59_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9085,14 +9085,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これ以上は望めません。それだけのこと</t>
+          <t xml:space="preserve">壁を作られている気がします。愉快ではありませんね</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9117,14 +9117,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">壁を作られている気がします。愉快ではありませんね</t>
+          <t xml:space="preserve">以前はもっと言葉を交わしていたはず。…何なのかしら</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">bond_60_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9149,14 +9149,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">以前はもっと言葉を交わしていたはず。…何なのかしら</t>
+          <t xml:space="preserve">良き仲間になれそうですわ。認めてあげます</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_80_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9181,14 +9181,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良き仲間になれそうですわ。認めてあげます</t>
+          <t xml:space="preserve">わたくしたち、最強のペアですわ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9213,14 +9213,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたち、最強のペアですわ</t>
+          <t xml:space="preserve">……もう、済んだこと</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9245,14 +9245,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、済んだこと</t>
+          <t xml:space="preserve">決着はつきました。次へ参ります</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9277,14 +9277,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着はつきました。次へ参ります</t>
+          <t xml:space="preserve">打ち負かすこと、楽しみにしておりますわ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9309,14 +9309,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">打ち負かすこと、楽しみにしておりますわ</t>
+          <t xml:space="preserve">打ち破ることが、わたくしの使命ですわ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9341,14 +9341,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">打ち破ることが、わたくしの使命ですわ</t>
+          <t xml:space="preserve">あの方がいたから強くなれました。感謝を…けれど負けません</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9373,14 +9373,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方がいたから強くなれました。感謝を…けれど負けません</t>
+          <t xml:space="preserve">この戦いは生涯続きます。望むところ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.ojousama[2]</t>
+          <t xml:space="preserve">trust_above_75.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9405,14 +9405,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この戦いは生涯続きます。望むところ</t>
+          <t xml:space="preserve">この団体の看板、わたくしが背負って差し上げますわ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.ojousama[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9437,14 +9437,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の看板、わたくしが背負って差し上げますわ</t>
+          <t xml:space="preserve">ふざけないでいただきたい。価値が分からぬなら、もう付き合いきれません</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.ojousama[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9469,14 +9469,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけないでいただきたい。価値が分からぬなら、もう付き合いきれません</t>
+          <t xml:space="preserve">この扱いは許せません。しかと覚えておくことです</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.ojousama[2]</t>
+          <t xml:space="preserve">trust_below_35.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9501,14 +9501,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱いは許せません。しかと覚えておくことです</t>
+          <t xml:space="preserve">わたくしの価値をご理解いただけていませんわね</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.ojousama[1]</t>
+          <t xml:space="preserve">GL-06.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9533,14 +9533,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの価値をご理解いただけていませんわね</t>
+          <t xml:space="preserve">わたくしの出番がないとは…運営の怠慢ですわ</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9565,14 +9565,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの出番がないとは…運営の怠慢ですわ</t>
+          <t xml:space="preserve">あの感覚は抜けてしまった？でも、得るものは十分でしたわ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9582,29 +9582,29 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの感覚は抜けてしまった？でも、得るものは十分でしたわ</t>
+          <t xml:space="preserve">傷の一つや二つ、どうということはありませんわ。最後まで、頂は渡しませんの</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.ojousama[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9629,14 +9629,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷の一つや二つ、どうということはありませんわ。最後まで、頂は渡しませんの</t>
+          <t xml:space="preserve">ここまで勝ち残ったのはわたくしですわ。締めくくりも、当然わたくしが</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.ojousama[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9661,14 +9661,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで勝ち残ったのはわたくしですわ。締めくくりも、当然わたくしが</t>
+          <t xml:space="preserve">次から次へと殊勝なこと。ですが、わたくしを越えるのは無理ですわ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.ojousama[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9693,14 +9693,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと殊勝なこと。ですが、わたくしを越えるのは無理ですわ</t>
+          <t xml:space="preserve">どなたがお相手でも、このリングの主はわたくしですのよ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.ojousama[2]</t>
+          <t xml:space="preserve">survivor.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9725,14 +9725,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どなたがお相手でも、このリングの主はわたくしですのよ</t>
+          <t xml:space="preserve">一人、片づけましたわ。…息は乱れていますけれど、まだまだですのよ。次はどなた?</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.ojousama[1]</t>
+          <t xml:space="preserve">survivor.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9757,14 +9757,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、片づけましたわ。…息は乱れていますけれど、まだまだですのよ。次はどなた?</t>
+          <t xml:space="preserve">このリングの主は、まだわたくしですわ。次の方、覚悟していらして</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.ojousama[2]</t>
+          <t xml:space="preserve">champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9789,14 +9789,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリングの主は、まだわたくしですわ。次の方、覚悟していらして</t>
+          <t xml:space="preserve">この三人が最強でしたわ。他に何か語る必要がありまして？</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">champion.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9821,14 +9821,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この三人が最強でしたわ。他に何か語る必要がありまして？</t>
+          <t xml:space="preserve">わたくしたち三人の前に、立てる団体はございませんでしたわね</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.ojousama[2]</t>
+          <t xml:space="preserve">defiant.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9853,14 +9853,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたち三人の前に、立てる団体はございませんでしたわね</t>
+          <t xml:space="preserve">お賞はいただきますわ。ですが……次は優勝旗もわたくしの手元に参りますのよ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.ojousama[1]</t>
+          <t xml:space="preserve">defiant.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9885,14 +9885,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お賞はいただきますわ。ですが……次は優勝旗もわたくしの手元に参りますのよ</t>
+          <t xml:space="preserve">わたくしを甘く見ないでくださいまし。次は、全てを奪い返しますわ</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.ojousama[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.ojousama[2]</t>
+          <t xml:space="preserve">gauntlet.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9917,14 +9917,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしを甘く見ないでくださいまし。次は、全てを奪い返しますわ</t>
+          <t xml:space="preserve">何人お相手しようと、わたくしを倒せなかった事実は変わりませんわ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.ojousama[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.ojousama[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9949,14 +9949,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人お相手しようと、わたくしを倒せなかった事実は変わりませんわ</t>
+          <t xml:space="preserve">次から次へと……けれど、このリングの主はわたくしでしたのよ</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9966,12 +9966,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.ojousama[2]</t>
+          <t xml:space="preserve">champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -9981,14 +9981,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと……けれど、このリングの主はわたくしでしたのよ</t>
+          <t xml:space="preserve">優勝はわたくしのもの。当然の結果ですわね</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.ojousama[1]</t>
+          <t xml:space="preserve">champion.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10013,14 +10013,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝はわたくしのもの。当然の結果ですわね</t>
+          <t xml:space="preserve">これがわたくしの実力。誰もかれもわかったかしら？</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.ojousama[2]</t>
+          <t xml:space="preserve">postLose.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10045,14 +10045,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これがわたくしの実力。誰もかれもわかったかしら？</t>
+          <t xml:space="preserve">こ、こんな結果…ありえないっ…！</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.bold.ojousama[1]</t>
+          <t xml:space="preserve">postLose.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10077,14 +10077,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんな結果…ありえないっ…！</t>
+          <t xml:space="preserve">わたくしともあろうものが…屈辱ですわ</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.bold.ojousama[2]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10109,14 +10109,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしともあろうものが…屈辱ですわ</t>
+          <t xml:space="preserve">当然の結果ね</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.bold.ojousama[1]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10141,14 +10141,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ね</t>
+          <t xml:space="preserve">この程度のことで驚いていては、私については来れなくてよ？</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.bold.ojousama[2]</t>
+          <t xml:space="preserve">postWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10173,14 +10173,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度のことで驚いていては、私については来れなくてよ？</t>
+          <t xml:space="preserve">私がこの程度で喜ぶとでも？…次こそ頂点を取りますわ</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.bold.ojousama[1]</t>
+          <t xml:space="preserve">postWin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10205,14 +10205,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私がこの程度で喜ぶとでも？…次こそ頂点を取りますわ</t>
+          <t xml:space="preserve">わたくしなら、この程度当然よ</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.bold.ojousama[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10237,14 +10237,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしなら、この程度当然よ</t>
+          <t xml:space="preserve">決勝は当然の舞台。このまま優勝もいただきましょう</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.ojousama[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10269,14 +10269,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝は当然の舞台。このまま優勝もいただきましょう</t>
+          <t xml:space="preserve">こいつが最後の獲物ね。覚悟は出来てるかしら</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.ojousama[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10301,14 +10301,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こいつが最後の獲物ね。覚悟は出来てるかしら</t>
+          <t xml:space="preserve">勝つのは私。それ以外のありえないでしょう？</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.ojousama[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10333,14 +10333,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝つのは私。それ以外のありえないでしょう？</t>
+          <t xml:space="preserve">格の違いを教えてあげる</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.ojousama[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.ojousama[2]</t>
+          <t xml:space="preserve">summon.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10365,14 +10365,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">格の違いを教えてあげる</t>
+          <t xml:space="preserve">私の選出は、当然ね</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.ojousama[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.bold.ojousama[1]</t>
+          <t xml:space="preserve">summon.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10397,14 +10397,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の選出は、当然ね</t>
+          <t xml:space="preserve">選ばれた以上、出場いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.ojousama[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10414,12 +10414,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10429,14 +10429,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選ばれた以上、出場いたしますわ</t>
+          <t xml:space="preserve">容赦は出来ないわ。覚悟する事ね</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10461,14 +10461,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">容赦は出来ないわ。覚悟する事ね</t>
+          <t xml:space="preserve">この座は渡せませんわね…… ずっと目指してきましたのよ……！</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10478,12 +10478,12 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10493,14 +10493,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この座は渡せませんわね…… ずっと目指してきましたのよ……！</t>
+          <t xml:space="preserve">そちらの団体のレベル、存じておりますわよ？</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.ojousama[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10515,7 +10515,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10525,14 +10525,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そちらの団体のレベル、存じておりますわよ？</t>
+          <t xml:space="preserve">格の違いをお教えして差し上げますわ</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.ojousama[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10542,12 +10542,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10557,14 +10557,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">格の違いをお教えして差し上げますわ</t>
+          <t xml:space="preserve">あらまあ。逃げ足が速い…格の違いは理解出来たみたいね</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.ojousama[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10589,14 +10589,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらまあ。逃げ足が速い…格の違いは理解出来たみたいね</t>
+          <t xml:space="preserve">うふふ……みっともないだこと。</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.ojousama[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10606,12 +10606,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">result_lose.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10621,14 +10621,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ……みっともないだこと。</t>
+          <t xml:space="preserve">嘘…こんな結果…認めませんわ…！</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.ojousama[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.bold.ojousama[1]</t>
+          <t xml:space="preserve">result_lose.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10653,14 +10653,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘…こんな結果…認めませんわ…！</t>
+          <t xml:space="preserve">次こそは…必ず…覚悟なさい！</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.ojousama[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.bold.ojousama[2]</t>
+          <t xml:space="preserve">result_win.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10685,14 +10685,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそは…必ず…覚悟なさい！</t>
+          <t xml:space="preserve">当然の結果ですわ。格の違い、おわかりになりまして？</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.ojousama[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.bold.ojousama[1]</t>
+          <t xml:space="preserve">result_win.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10717,14 +10717,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ですわ。格の違い、おわかりになりまして？</t>
+          <t xml:space="preserve">圧勝ですわね。ふふっ</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.ojousama[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10749,14 +10749,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">圧勝ですわね。ふふっ</t>
+          <t xml:space="preserve">当然の結果ね。……私を甘く見るべきじゃなかったわね</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10781,14 +10781,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ね。……私を甘く見るべきじゃなかったわね</t>
+          <t xml:space="preserve">この程度で終わりではなくてよ</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.ojousama[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10813,14 +10813,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で終わりではなくてよ</t>
+          <t xml:space="preserve">私の団体に挑むなど……百年早いですわね</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.ojousama[3]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10830,29 +10830,29 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[3]</t>
+          <t xml:space="preserve">fighter.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の団体に挑むなど……百年早いですわね</t>
+          <t xml:space="preserve">これが頂点の景色？…馬鹿ね。まだまだ先はあってよ</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.bold.ojousama[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10862,29 +10862,29 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これが頂点の景色？…馬鹿ね。まだまだ先はあってよ</t>
+          <t xml:space="preserve">チャンスをありがとう。私を侮ったあいつらに、ほえ面かかせてやりますわ</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.bold.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10909,44 +10909,12 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンスをありがとう。私を侮ったあいつらに、ほえ面かかせてやりますわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="333" ht="40" customHeight="1">
-      <c r="A333" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.bold.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">bold.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">あら、お目が高いわね。わたくしに気づくなんて</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H333"/>
+  <autoFilter ref="A1:H332"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×強気.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H332"/>
+  <dimension ref="A1:H334"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">捨てられた者の方が上でしたわ。ご覧いただけまして?</t>
+          <t xml:space="preserve">捨てられた者の方が上でしたわ。ご覧いただけまして？</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めない……！ この借りは……必ず返す……！</t>
+          <t xml:space="preserve">……今日のところは、預けておくわ。次は同じ景色ではないでしょうね</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">名指しさせていただくわ。あの相手との舞台、整えられる?</t>
+          <t xml:space="preserve">名指しさせていただくわ。あの相手との舞台、整えられる？</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしい。お受けします。覚悟はおありで?</t>
+          <t xml:space="preserve">よろしい。お受けします。覚悟はおありで？</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身の程は分かりました? …ふふ。</t>
+          <t xml:space="preserve">身の程は分かりました？ …ふふ。</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">女王である私を引退させようなんて、100年早くてよ</t>
+          <t xml:space="preserve">女王である私を引退させようなんて、百年早くてよ</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねぇ社長、次のメイン、わたくしたちにお任せいただけませんこと?</t>
+          <t xml:space="preserve">ねぇ社長、次のメイン、わたくしたちにお任せいただけませんこと？</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねぇ社長、わたくしどもの給与、改めてお考えいただけませんこと?</t>
+          <t xml:space="preserve">ねぇ社長、わたくしどもの給与、改めてお考えいただけませんこと？</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねぇ社長、わたくしどもの貢献、きちんと評価していただいておりますの?</t>
+          <t xml:space="preserve">ねぇ社長、わたくしどもの貢献、きちんと評価していただいておりますの？</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等ですわ。お受けいたしましょう</t>
+          <t xml:space="preserve">よろしくてよ。お受けいたしましょう</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目が覚めたわ。ここで終わるわけにはかないもの</t>
+          <t xml:space="preserve">目が覚めたわ。ここで終わるわけにはいかないもの</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6180,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.ojousama.bold[1]</t>
+          <t xml:space="preserve">autumnWarChampion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6205,14 +6205,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方と全力で戦えたことは、大変名誉ですわ</t>
+          <t xml:space="preserve">わたくしたちの団体が最強だと、証明できましたわね。</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.ojousama.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.bold[1]</t>
+          <t xml:space="preserve">bestMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6237,14 +6237,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この王座はわたくしに最もふさわしい。それを証明し続けますわ</t>
+          <t xml:space="preserve">あの方と全力で戦えたことは、大変名誉ですわ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.ojousama.bold[1]</t>
+          <t xml:space="preserve">champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6269,14 +6269,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの名が歴史に刻まれる。…ふさわしいと、自分で思えますわ</t>
+          <t xml:space="preserve">この王座はわたくしに最もふさわしい。それを証明し続けますわ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.ojousama.bold[1]</t>
+          <t xml:space="preserve">hallOfFame.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6301,14 +6301,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしが最も輝いた一年でしたわね。異論のある方はリングでお待ちしています</t>
+          <t xml:space="preserve">わたくしの名が歴史に刻まれる。…ふさわしいと、自分で思えますわ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.ojousama.bold[1]</t>
+          <t xml:space="preserve">mvp.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6333,14 +6333,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ですわね。わたくしの実力を見れば、誰もが納得するでしょう？</t>
+          <t xml:space="preserve">わたくしが最も輝いた一年でしたわね。異論のある方はリングでお待ちしています</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">rookie.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6365,14 +6365,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドームですわよ!! 思い切り暴れますわ!</t>
+          <t xml:space="preserve">当然の結果ですわね。わたくしの実力を見れば、誰もが納得するでしょう？</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">springTagChampion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6397,14 +6397,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほほほ、わたくしの本気、ご覧に入れましょう!</t>
+          <t xml:space="preserve">わたくしたちの連係に、並のタッグが届くはずもありませんわ。</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[3]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6429,14 +6429,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリング、わたくしの独壇場にしてみせますわ!</t>
+          <t xml:space="preserve">ドーム。……ようやく、相応しい場所ね</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6461,14 +6461,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員ですって!? 胸が熱くなりますわ!!</t>
+          <t xml:space="preserve">ほほほ、わたくしの本気、ご覧に入れましょう！</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6493,14 +6493,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様方の歓声、まだ耳に焼き付いておりますの!</t>
+          <t xml:space="preserve">このリング、わたくしの独壇場にしてみせますわ！</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[3]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6525,14 +6525,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この勢い、止めてはなりませんわよ!!</t>
+          <t xml:space="preserve">満員……ふふ、当然でしょうね。この顔ぶれですもの</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6542,29 +6542,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだですわ。もっと上を目指しませんと…</t>
+          <t xml:space="preserve">お客様方の歓声、まだ耳に焼き付いておりますの！</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6574,29 +6574,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様のご期待が、わたくしの力になっておりますわ</t>
+          <t xml:space="preserve">この勢い、止めてはなりませんわよ！！</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.ojousama.bold[1]</t>
+          <t xml:space="preserve">N1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6621,14 +6621,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度、問題ありませんわ</t>
+          <t xml:space="preserve">まだまだですわ。もっと上を目指しませんと…</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.ojousama.bold[1]</t>
+          <t xml:space="preserve">N2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6653,14 +6653,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この声援を力に、さらに上を目指しますわ</t>
+          <t xml:space="preserve">皆様のご期待が、わたくしの力になっておりますわ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.ojousama.bold[1]</t>
+          <t xml:space="preserve">N3.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6685,14 +6685,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この団体で、わたしの夢は叶えられますの…？</t>
+          <t xml:space="preserve">この程度、問題ありませんわ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.ojousama.bold[1]</t>
+          <t xml:space="preserve">N4.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6717,14 +6717,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままで本当によろしいのか、と考えてしまいますの</t>
+          <t xml:space="preserve">この声援を力に、さらに上を目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.ojousama.bold[1]</t>
+          <t xml:space="preserve">N5_low.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6749,14 +6749,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わたくしの価値、ちゃんと見てくださっているのかしら</t>
+          <t xml:space="preserve">…この団体で、私の夢は叶えられますの…？</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.ojousama.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.ojousama.bold[1]</t>
+          <t xml:space="preserve">N5_warning.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6781,14 +6781,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わたくしにふさわしい舞台がまだ来ないなんて</t>
+          <t xml:space="preserve">…このままで本当によろしいのか、と考えてしまいますの</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.ojousama.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6798,29 +6798,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.ojousama.bold[1]</t>
+          <t xml:space="preserve">G1.voice.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お断りしますわ。わたくしの価値は、この程度ではありませんの</t>
+          <t xml:space="preserve">…わたくしの価値、ちゃんと見てくださっているのかしら</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6830,29 +6830,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.ojousama.bold[1]</t>
+          <t xml:space="preserve">G3.voice.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。結果でお返しするわ</t>
+          <t xml:space="preserve">…わたくしにふさわしい舞台がまだ来ないなんて</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.ojousama.bold[1]</t>
+          <t xml:space="preserve">bonus_insult.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6877,14 +6877,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この合宿で一段上へ参りましょう</t>
+          <t xml:space="preserve">お断りしますわ。わたくしの価値は、この程度ではありませんの</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.ojousama.bold[1]</t>
+          <t xml:space="preserve">bonus.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6909,14 +6909,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが信じているなら、応えてあげないとかしらね？</t>
+          <t xml:space="preserve">ありがとうございます。結果でお返しするわ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.ojousama.bold[1]</t>
+          <t xml:space="preserve">camp.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6941,14 +6941,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなところで終わりませんわ！</t>
+          <t xml:space="preserve">この合宿で一段上へ参りましょう</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.ojousama.bold[1]</t>
+          <t xml:space="preserve">encourage_high_trust.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6973,14 +6973,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">納得はしておりません。そこだけは、申し上げておきます</t>
+          <t xml:space="preserve">あなたが信じているなら、応えてあげませんとね？</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.ojousama.bold[1]</t>
+          <t xml:space="preserve">encourage.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7005,14 +7005,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">より広い舞台へということね。当然ね。</t>
+          <t xml:space="preserve">こんなところで終わりませんわ！</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.ojousama.bold[1]</t>
+          <t xml:space="preserve">faction_decree.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7037,14 +7037,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様の頑張りを、誇りに思いますわ</t>
+          <t xml:space="preserve">納得はしておりません。そこだけは、申し上げておきます</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.ojousama.bold[1]</t>
+          <t xml:space="preserve">media.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7069,14 +7069,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すこし休んでまいりますわ。ごめんあそばせ。</t>
+          <t xml:space="preserve">より広い舞台へということね。当然ね。</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.ojousama.bold[1]</t>
+          <t xml:space="preserve">party.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7101,14 +7101,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐ戻ります。待っていなさいな。</t>
+          <t xml:space="preserve">皆様の頑張りを、誇りに思いますわ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.ojousama.bold[1]</t>
+          <t xml:space="preserve">refresh_leave.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7133,14 +7133,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この機会、決して無駄にはしない</t>
+          <t xml:space="preserve">すこし休んでまいりますわ。ごめんあそばせ。</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.ojousama.bold[1]</t>
+          <t xml:space="preserve">special_treatment.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7165,14 +7165,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が出ればお客様も喜ぶでしょうね。楽しみだわ…</t>
+          <t xml:space="preserve">すぐ戻ります。待っていなさいな。</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.ojousama.bold[1]</t>
+          <t xml:space="preserve">trainer.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7197,14 +7197,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…正直に申しますと、良い条件ですわ</t>
+          <t xml:space="preserve">この機会、決して無駄にはしない</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.ojousama.bold[1]</t>
+          <t xml:space="preserve">E1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7229,14 +7229,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習…？ 出していただけないのに、意味がありますか</t>
+          <t xml:space="preserve">私が出ればお客様も喜ぶでしょうね。楽しみだわ…</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.bold[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.ojousama.bold[2]</t>
+          <t xml:space="preserve">E6.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7261,14 +7261,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングに上がれないのなら、稽古など無駄でしょう</t>
+          <t xml:space="preserve">…正直に申しますと、良い条件ですわ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.ojousama.bold[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7293,14 +7293,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「なぜわたくしたちがこんな扱いを受けねばならないの」と控室で声を張っている）</t>
+          <t xml:space="preserve">練習…？ 出していただけないのに、意味がありますか</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.ojousama.bold[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7325,14 +7325,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「このまま終わるつもりはございません」と宣言めいた投稿）</t>
+          <t xml:space="preserve">リングに上がれないのなら、稽古など無駄でしょう</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.ojousama.bold[1]</t>
+          <t xml:space="preserve">S_grumble.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7357,14 +7357,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンの座、いただきに参りましょう</t>
+          <t xml:space="preserve">（「この扱いの意味、伺いたいものね」と控室で静かに笑ってみせる）</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.ojousama.bold[1]</t>
+          <t xml:space="preserve">S_sns.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7389,14 +7389,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれとも決着をつけませんとね……</t>
+          <t xml:space="preserve">（SNSに「このまま終わるつもりはございません」と宣言めいた投稿）</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.ojousama.bold[1]</t>
+          <t xml:space="preserve">S1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7421,14 +7421,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…情けないけれど、もう、体が限界ですわね</t>
+          <t xml:space="preserve">チャンピオンの座、いただきに参りましょう</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.ojousama.bold[1]</t>
+          <t xml:space="preserve">S2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7453,14 +7453,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは納得できませんわね。……どうするか、考えなさいね？</t>
+          <t xml:space="preserve">あれとも決着をつけませんとね……</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.ojousama.bold[1]</t>
+          <t xml:space="preserve">S3.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7485,14 +7485,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（膝の上で、手を固く握りしめている）</t>
+          <t xml:space="preserve">…情けないけれど、もう、体が限界ですわね</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.ojousama.bold[1]</t>
+          <t xml:space="preserve">S4_direct.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7517,14 +7517,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと上を目指す為に。特訓が必要ね…</t>
+          <t xml:space="preserve">このままでは納得できませんわね。……どうするか、考えなさいね？</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.ojousama.bold[1]</t>
+          <t xml:space="preserve">S4_silent.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7549,14 +7549,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">若手の面倒を見るのも、私の務めですわね</t>
+          <t xml:space="preserve">…………（膝の上で、手を固く握りしめている）</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7566,12 +7566,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.ojousama.bold[1]</t>
+          <t xml:space="preserve">S5.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなところで止まるわけにはいかないわ…</t>
+          <t xml:space="preserve">もっと上を目指す為に。特訓が必要ね…</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7598,12 +7598,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.ojousama.bold[1]</t>
+          <t xml:space="preserve">S6.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7613,14 +7613,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの女の態度は許せないわね……</t>
+          <t xml:space="preserve">若手の面倒を見るのも、私の務めですわね</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.ojousama.bold[1]</t>
+          <t xml:space="preserve">B1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7645,14 +7645,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私も黙ってはいられませんわ。あちらに非があるのだから</t>
+          <t xml:space="preserve">こんなところで止まるわけにはいかないわ…</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.ojousama.bold[1]</t>
+          <t xml:space="preserve">B2_fighter1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7677,14 +7677,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私なら、確かにブランドイメージは上がるでしょうね</t>
+          <t xml:space="preserve">あの女の態度は許せないわね……</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.ojousama.bold[1]</t>
+          <t xml:space="preserve">B2_fighter2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7709,14 +7709,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM？仕方ないわね……品と格というものを知らしめなければ</t>
+          <t xml:space="preserve">私も黙ってはいられませんわ。あちらに非があるのだから</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.ojousama.bold[1]</t>
+          <t xml:space="preserve">B4_brand.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7741,14 +7741,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方々に最高の時間をお届けしますわ</t>
+          <t xml:space="preserve">私なら、確かにブランドイメージは上がるでしょうね</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.ojousama.bold[1]</t>
+          <t xml:space="preserve">B4_cm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7773,14 +7773,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイね……もちろん自信はあるわよ？</t>
+          <t xml:space="preserve">CM？仕方ないわね……品と格というものを知らしめなければ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.ojousama.bold[1]</t>
+          <t xml:space="preserve">B4_fan.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7805,14 +7805,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">撮影？私の魅力を引き出せるのかしら？</t>
+          <t xml:space="preserve">ファンの方々に最高の時間をお届けしますわ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.ojousama.bold[1]</t>
+          <t xml:space="preserve">B4_fashion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7837,14 +7837,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">トーク番組？妙な仕事を持ってくるものね</t>
+          <t xml:space="preserve">ランウェイね……もちろん自信はあるわよ？</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.ojousama.bold[1]</t>
+          <t xml:space="preserve">B4_gravure.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7869,14 +7869,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、全国の皆様も私の事が気にかかるのかしら？</t>
+          <t xml:space="preserve">撮影？私の魅力を引き出せるのかしら？</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7886,29 +7886,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">B4_variety.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
+          <t xml:space="preserve">トーク番組？妙な仕事を持ってくるものね</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7918,29 +7918,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">B4.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">あらあら、全国の皆様も私の事が気にかかるのかしら？</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.bold[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7965,14 +7965,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんに立ちますわよ。当然ですの</t>
+          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
@@ -7997,14 +7997,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8029,14 +8029,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
+          <t xml:space="preserve">頂点に立ちますわよ。当然ですの</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
@@ -8061,14 +8061,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
+          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.bold[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8093,14 +8093,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を止めるには足りませんわよ</t>
+          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8125,14 +8125,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">倒した相手と同じ列に並ばされる屈辱、分かるかしらね？</t>
+          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8157,14 +8157,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">幕を引かれた側の気持ちは、誰も聞きませんのね</t>
+          <t xml:space="preserve">私を止めるには足りませんわよ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.ojousama.bold[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8189,14 +8189,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
+          <t xml:space="preserve">倒した相手と同じ列に並ばされる屈辱、分かるかしらね？</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.bold[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8221,14 +8221,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">幕を引かれた側の気持ちは、誰も聞きませんのね</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.bold[2]</t>
+          <t xml:space="preserve">draftInterest.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8253,14 +8253,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんに立ちますわよ。当然ですの</t>
+          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.ojousama.bold[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8285,14 +8285,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンスをありがとう。私を侮ったあいつらに、ほえ面かかせてやりますわ</t>
+          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.ojousama.bold[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8317,14 +8317,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">頂点に立ちますわよ。当然ですの</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.ojousama.bold[1]</t>
+          <t xml:space="preserve">faGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8349,14 +8349,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
+          <t xml:space="preserve">良い機会をいただいたわ。私を見誤った方々に、答えを見せるとしましょう</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.ojousama.bold[1]</t>
+          <t xml:space="preserve">faSigning.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8381,14 +8381,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は調子がいいの。手加減は無用ですわね</t>
+          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.ojousama.bold[1]</t>
+          <t xml:space="preserve">faWelcome.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8413,14 +8413,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は重いですけれど。…認めるつもりはありません</t>
+          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.ojousama.bold[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8445,14 +8445,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ動けます。…少し、体が言うことを聞きませんが</t>
+          <t xml:space="preserve">今日は調子がいいの。手加減は無用ですわね</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.ojousama.bold[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8477,14 +8477,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
+          <t xml:space="preserve">体は重いですけれど。…認めるつもりはありません</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.ojousama.bold[2]</t>
+          <t xml:space="preserve">heatSelf.warm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を止めるには足りませんわよ</t>
+          <t xml:space="preserve">まだ動けます。…少し、体が言うことを聞きませんが</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.ojousama.bold[1]</t>
+          <t xml:space="preserve">injury.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8541,14 +8541,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
+          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.ojousama.bold[2]</t>
+          <t xml:space="preserve">injury.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8573,14 +8573,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで終わりではありませんわよ</t>
+          <t xml:space="preserve">私を止めるには足りませんわよ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.ojousama.bold[1]</t>
+          <t xml:space="preserve">release.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8605,14 +8605,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
+          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.ojousama.bold[1]</t>
+          <t xml:space="preserve">release.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8637,14 +8637,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、お目が高いわね。わたくしに気づくなんて</t>
+          <t xml:space="preserve">これで終わりではありませんわよ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.ojousama.bold[1]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8669,14 +8669,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ…！もう一度お願いいたします！</t>
+          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.ojousama.bold[1]</t>
+          <t xml:space="preserve">scoutGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8701,14 +8701,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもお譲りしませんわ。もっと上を目指しますの</t>
+          <t xml:space="preserve">あら、お目が高いわね。わたくしに気づくなんて</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.ojousama.bold[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8733,14 +8733,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ…！必ず取り返しますの！</t>
+          <t xml:space="preserve">……これで終わりかしら。もう一度、場を用意していただける？</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.ojousama.bold[1]</t>
+          <t xml:space="preserve">titleDefense.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8765,14 +8765,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちましたわ。でもここからが本当の闘いですの</t>
+          <t xml:space="preserve">まだ誰にもお譲りしませんわ。もっと上を目指しますの</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">titleLoss.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8797,14 +8797,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
+          <t xml:space="preserve">認めませんわ…！必ず取り返しますの！</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">titleWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8829,14 +8829,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで終わりではありませんわよ</t>
+          <t xml:space="preserve">頂点に立ちましたわ。でもここからが本当の闘いですの</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
@@ -8861,14 +8861,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
+          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8893,14 +8893,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ…！もう一度お願いいたします！</t>
+          <t xml:space="preserve">これで終わりではありませんわよ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
@@ -8925,14 +8925,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもお譲りしませんわ。もっと上を目指しますの</t>
+          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
@@ -8957,14 +8957,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ…！必ず取り返しますの！</t>
+          <t xml:space="preserve">……これで終わりかしら。もう一度、場を用意していただける？</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
@@ -8989,14 +8989,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちましたわ。でもここからが本当の闘いですの</t>
+          <t xml:space="preserve">まだ誰にもお譲りしませんわ。もっと上を目指しますの</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9006,29 +9006,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合いません。どうしても</t>
+          <t xml:space="preserve">認めませんわ…！必ず取り返しますの！</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9038,29 +9038,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これ以上は望めません。それだけのこと</t>
+          <t xml:space="preserve">頂点に立ちましたわ。でもここからが本当の闘いですの</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9085,14 +9085,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">壁を作られている気がします。愉快ではありませんね</t>
+          <t xml:space="preserve">合いません。どうしても</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">bond_39_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9117,14 +9117,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">以前はもっと言葉を交わしていたはず。…何なのかしら</t>
+          <t xml:space="preserve">これ以上は望めません。それだけのこと</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9149,14 +9149,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良き仲間になれそうですわ。認めてあげます</t>
+          <t xml:space="preserve">壁を作られている気がします。愉快ではありませんね</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9181,14 +9181,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたち、最強のペアですわ</t>
+          <t xml:space="preserve">以前はもっと言葉を交わしていたはず。…何なのかしら</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_60_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9213,14 +9213,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、済んだこと</t>
+          <t xml:space="preserve">良き仲間になれそうですわ。認めてあげます</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">bond_80_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9245,14 +9245,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着はつきました。次へ参ります</t>
+          <t xml:space="preserve">わたくしたち、最強のペアですわ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9277,14 +9277,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">打ち負かすこと、楽しみにしておりますわ</t>
+          <t xml:space="preserve">……もう、済んだこと</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9309,14 +9309,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">打ち破ることが、わたくしの使命ですわ</t>
+          <t xml:space="preserve">決着はつきました。次へ参ります</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9341,14 +9341,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方がいたから強くなれました。感謝を…けれど負けません</t>
+          <t xml:space="preserve">打ち負かすこと、楽しみにしておりますわ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9373,14 +9373,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この戦いは生涯続きます。望むところ</t>
+          <t xml:space="preserve">打ち破ることが、わたくしの使命ですわ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9405,14 +9405,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の看板、わたくしが背負って差し上げますわ</t>
+          <t xml:space="preserve">あの方がいたから強くなれました。感謝を…けれど負けません</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9437,14 +9437,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけないでいただきたい。価値が分からぬなら、もう付き合いきれません</t>
+          <t xml:space="preserve">この戦いは生涯続きます。望むところ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.ojousama[2]</t>
+          <t xml:space="preserve">trust_above_75.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9469,14 +9469,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱いは許せません。しかと覚えておくことです</t>
+          <t xml:space="preserve">この団体の看板、わたくしが背負って差し上げますわ</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.ojousama[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9501,14 +9501,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの価値をご理解いただけていませんわね</t>
+          <t xml:space="preserve">ふざけないでいただきたい。価値が分からぬなら、もう付き合いきれません</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.ojousama.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.ojousama.bold[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9533,14 +9533,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの出番がないとは…運営の怠慢ですわ</t>
+          <t xml:space="preserve">この扱いは許せません。しかと覚えておくことです</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9565,14 +9565,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの感覚は抜けてしまった？でも、得るものは十分でしたわ</t>
+          <t xml:space="preserve">わたくしの価値をご理解いただけていませんわね</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9582,29 +9582,29 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.bold[1]</t>
+          <t xml:space="preserve">GL-06.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷の一つや二つ、どうということはありませんわ。最後まで、頂は渡しませんの</t>
+          <t xml:space="preserve">わたくしの出番がないとは…運営の怠慢ですわ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9614,29 +9614,29 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.bold[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで勝ち残ったのはわたくしですわ。締めくくりも、当然わたくしが</t>
+          <t xml:space="preserve">あの感覚は抜けてしまった？でも、得るものは十分でしたわ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.bold[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9661,14 +9661,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと殊勝なこと。ですが、わたくしを越えるのは無理ですわ</t>
+          <t xml:space="preserve">傷の一つや二つ、どうということはありませんわ。最後まで、頂は渡しませんの</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.bold[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9693,14 +9693,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どなたがお相手でも、このリングの主はわたくしですのよ</t>
+          <t xml:space="preserve">ここまで勝ち残ったのはわたくしですわ。締めくくりも、当然わたくしが</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.bold[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9725,14 +9725,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、片づけましたわ。…息は乱れていますけれど、まだまだですのよ。次はどなた?</t>
+          <t xml:space="preserve">次から次へと殊勝なこと。ですが、わたくしを越えるのは無理ですわ</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.bold[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9757,14 +9757,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリングの主は、まだわたくしですわ。次の方、覚悟していらして</t>
+          <t xml:space="preserve">どなたがお相手でも、このリングの主はわたくしですのよ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.bold[1]</t>
+          <t xml:space="preserve">survivor.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9789,14 +9789,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この三人が最強でしたわ。他に何か語る必要がありまして？</t>
+          <t xml:space="preserve">一人、片づけましたわ。…息は乱れていますけれど、まだまだですのよ。次はどなた？</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.bold[2]</t>
+          <t xml:space="preserve">survivor.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9821,14 +9821,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたち三人の前に、立てる団体はございませんでしたわね</t>
+          <t xml:space="preserve">このリングの主は、まだわたくしですわ。次の方、覚悟していらして</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.bold[1]</t>
+          <t xml:space="preserve">champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9853,14 +9853,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お賞はいただきますわ。ですが……次は優勝旗もわたくしの手元に参りますのよ</t>
+          <t xml:space="preserve">この三人が最強でしたわ。他に何か語る必要がありまして？</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.bold[2]</t>
+          <t xml:space="preserve">champion.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9885,14 +9885,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしを甘く見ないでくださいまし。次は、全てを奪い返しますわ</t>
+          <t xml:space="preserve">わたくしたち三人の前に、立てる団体はございませんでしたわね</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.bold[1]</t>
+          <t xml:space="preserve">defiant.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9917,14 +9917,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人お相手しようと、わたくしを倒せなかった事実は変わりませんわ</t>
+          <t xml:space="preserve">賞はいただきますわ。ですが……次は優勝旗もわたくしの手元に参りますのよ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.bold[2]</t>
+          <t xml:space="preserve">defiant.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9949,14 +9949,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと……けれど、このリングの主はわたくしでしたのよ</t>
+          <t xml:space="preserve">わたくしを甘く見ないでくださいまし。次は、全てを奪い返しますわ</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9966,12 +9966,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.bold[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -9981,14 +9981,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝はわたくしのもの。当然の結果ですわね</t>
+          <t xml:space="preserve">何人お相手しようと、わたくしを倒せなかった事実は変わりませんわ</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -9998,12 +9998,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.bold[2]</t>
+          <t xml:space="preserve">gauntlet.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10013,14 +10013,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これがわたくしの実力。誰もかれもわかったかしら？</t>
+          <t xml:space="preserve">次から次へと……けれど、このリングの主はわたくしでしたのよ</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.ojousama.bold[1]</t>
+          <t xml:space="preserve">champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10045,14 +10045,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こ、こんな結果…ありえないっ…！</t>
+          <t xml:space="preserve">優勝はわたくしのもの。当然の結果ですわね</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.ojousama.bold[2]</t>
+          <t xml:space="preserve">champion.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10077,14 +10077,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしともあろうものが…屈辱ですわ</t>
+          <t xml:space="preserve">これがわたくしの実力。誰もかれもわかったかしら？</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.ojousama.bold[1]</t>
+          <t xml:space="preserve">postLose.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10109,14 +10109,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ね</t>
+          <t xml:space="preserve">……これが結果？ ……信じられないわね</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.ojousama.bold[2]</t>
+          <t xml:space="preserve">postLose.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10141,14 +10141,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度のことで驚いていては、私については来れなくてよ？</t>
+          <t xml:space="preserve">わたくしともあろうものが…屈辱ですわ</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.ojousama.bold[1]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10173,14 +10173,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私がこの程度で喜ぶとでも？…次こそ頂点を取りますわ</t>
+          <t xml:space="preserve">当然の結果ね</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.ojousama.bold[2]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10205,14 +10205,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしなら、この程度当然よ</t>
+          <t xml:space="preserve">この程度のことで驚いていては、私についてはこられなくてよ？</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.bold[1]</t>
+          <t xml:space="preserve">postWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10237,14 +10237,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝は当然の舞台。このまま優勝もいただきましょう</t>
+          <t xml:space="preserve">私がこの程度で喜ぶとでも？…次こそ頂点を取りますわ</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.bold[2]</t>
+          <t xml:space="preserve">postWin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10269,14 +10269,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こいつが最後の獲物ね。覚悟は出来てるかしら</t>
+          <t xml:space="preserve">わたくしなら、この程度当然よ</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.bold[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10301,14 +10301,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝つのは私。それ以外のありえないでしょう？</t>
+          <t xml:space="preserve">決勝は当然の舞台。このまま優勝もいただきましょう</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.bold[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10333,14 +10333,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">格の違いを教えてあげる</t>
+          <t xml:space="preserve">あなたで最後ね。……覚悟はできているのかしら</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.ojousama.bold[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10365,14 +10365,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の選出は、当然ね</t>
+          <t xml:space="preserve">勝つのは私。それ以外ありえないでしょう？</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.ojousama.bold[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10397,14 +10397,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選ばれた以上、出場いたしますわ</t>
+          <t xml:space="preserve">格の違いを教えてあげる</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10414,12 +10414,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">summon.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10429,14 +10429,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">容赦は出来ないわ。覚悟する事ね</t>
+          <t xml:space="preserve">私の選出は、当然ね</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">summon.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10461,14 +10461,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この座は渡せませんわね…… ずっと目指してきましたのよ……！</t>
+          <t xml:space="preserve">選ばれた以上、出場いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.bold[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
@@ -10493,14 +10493,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そちらの団体のレベル、存じておりますわよ？</t>
+          <t xml:space="preserve">容赦は出来ないわ。覚悟する事ね</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.bold[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10525,14 +10525,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">格の違いをお教えして差し上げますわ</t>
+          <t xml:space="preserve">この座は渡せませんわね…… ずっと目指してきましたのよ……！</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
@@ -10557,14 +10557,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらまあ。逃げ足が速い…格の違いは理解出来たみたいね</t>
+          <t xml:space="preserve">そちらの団体のレベル、存じておりますわよ？</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.bold[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
@@ -10589,14 +10589,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ……みっともないだこと。</t>
+          <t xml:space="preserve">格の違いをお教えして差し上げますわ</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.bold[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10606,12 +10606,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10621,14 +10621,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘…こんな結果…認めませんわ…！</t>
+          <t xml:space="preserve">あらまあ。逃げ足が速い…格の違いは理解出来たみたいね</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.bold[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10638,12 +10638,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.ojousama.bold[2]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10653,14 +10653,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそは…必ず…覚悟なさい！</t>
+          <t xml:space="preserve">うふふ……みっともないこと。</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.ojousama.bold[1]</t>
+          <t xml:space="preserve">result_lose.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10685,14 +10685,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ですわ。格の違い、おわかりになりまして？</t>
+          <t xml:space="preserve">嘘…こんな結果…認めませんわ…！</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.bold[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.ojousama.bold[2]</t>
+          <t xml:space="preserve">result_lose.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10717,14 +10717,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">圧勝ですわね。ふふっ</t>
+          <t xml:space="preserve">次こそは…必ず…覚悟なさい！</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">result_win.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10749,14 +10749,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ね。……私を甘く見るべきじゃなかったわね</t>
+          <t xml:space="preserve">当然の結果ですわ。格の違い、おわかりになりまして？</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">result_win.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10781,14 +10781,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で終わりではなくてよ</t>
+          <t xml:space="preserve">圧勝ですわね。ふふっ</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[3]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10813,14 +10813,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の団体に挑むなど……百年早いですわね</t>
+          <t xml:space="preserve">当然の結果ね。……私を甘く見るべきではなかったわね</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.bold[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10830,29 +10830,29 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これが頂点の景色？…馬鹿ね。まだまだ先はあってよ</t>
+          <t xml:space="preserve">この程度で終わりではなくてよ</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10862,59 +10862,123 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンスをありがとう。私を侮ったあいつらに、ほえ面かかせてやりますわ</t>
+          <t xml:space="preserve">私の団体に挑むなど……百年早いですわね</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">これが頂点の景色……？ ……ふふ、まだ先があるでしょうね</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="40" customHeight="1">
+      <c r="A333" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">良い機会をいただいたわ。私を見誤った方々に、答えを見せるとしましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="40" customHeight="1">
+      <c r="A334" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.ojousama.bold[1]</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr" s="2">
+      <c r="B334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr" s="12">
+      <c r="D334" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr" s="2">
+      <c r="E334" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr" s="3">
+      <c r="F334" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あら、お目が高いわね。わたくしに気づくなんて</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H332"/>
+  <autoFilter ref="A1:H334"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×強気.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H334"/>
+  <dimension ref="A1:H341"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3872,7 +3872,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.ojousama.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.ojousama.bold[1]</t>
+          <t xml:space="preserve">decline_accept.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3897,14 +3897,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……理解が早いわね。この評価に見合う結果を期待していなさい。</t>
+          <t xml:space="preserve">よろしくてよ。……その額でどれほどのものが手に入るか、ご覧になって</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.ojousama.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.ojousama.bold[1]</t>
+          <t xml:space="preserve">decline_hold.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3929,14 +3929,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今はこういう評価という事ね。次はきちんとした評価を期待しますわ。</t>
+          <t xml:space="preserve">……下げない、と？ ……見る目だけはおありのようね。恥はかかせませんわ</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.ojousama.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.ojousama.bold[1]</t>
+          <t xml:space="preserve">decline_open.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……左様ですか。ですが社長、次はありませんわよ。</t>
+          <t xml:space="preserve">……値札のお話ね。ふふ、下げるのはご自由に。……私の格まで下がるわけじゃないもの</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.ojousama.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.ojousama.bold[1]</t>
+          <t xml:space="preserve">decline_strict.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -3993,14 +3993,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}申し上げにくいのですが、この待遇はわたくしに見合いませんわ。{record}</t>
+          <t xml:space="preserve">……そこまでなさるの。ふふ、覚えておきますわ。……勘定は、いずれ</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.ojousama.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.ojousama.bold[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………。そうですか。わたくしにも限度というものがありますのよ？</t>
+          <t xml:space="preserve">潔くて結構。……次に値をつけ直すとき、そちらが慌てることになるわね</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.ojousama.bold[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4057,14 +4057,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、もう無理ですわ。お世話になりました……と申し上げたいところですけれど、正直そうも思えませんの。</t>
+          <t xml:space="preserve">……わたくしの申し出を退けるなんて、いいご身分になったのね。ふふ……頼りにされているなら、それに応えようかしら？</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.bold[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.ojousama.bold[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう決めました。これ以上ここに留まる理由がありません。ごきげんよう。</t>
+          <t xml:space="preserve">社長。年俸は下げてくださって結構よ。……以前と同額を受け取るわけにもいかないわ</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.ojousama.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.ojousama.bold[1]</t>
+          <t xml:space="preserve">raise_accept.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4121,14 +4121,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……聞いてくださるの。{record}わたくし、もっと上の舞台を求めておりますの。</t>
+          <t xml:space="preserve">……理解が早いわね。この評価に見合う結果を期待していなさい。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.ojousama.bold[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4153,14 +4153,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}決心がつきましたの。わたくし、この団体を去りますわ。</t>
+          <t xml:space="preserve">……今はこういう評価という事ね。次はきちんとした評価を期待しますわ。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.ojousama.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.ojousama.bold[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4185,14 +4185,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふふ。予想通りですわ。{rivalry}ごきげんよう、社長。</t>
+          <t xml:space="preserve">……左様ですか。ですが社長、次はありませんわよ。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.ojousama.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.ojousama.bold[1]</t>
+          <t xml:space="preserve">raise_open.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4217,14 +4217,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今更。　……もう心は決まっているわ</t>
+          <t xml:space="preserve">社長。{tenure}申し上げにくいのですが、この待遇はわたくしに見合いませんわ。{record}</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.ojousama.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.ojousama.bold[1]</t>
+          <t xml:space="preserve">raise_refuse.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4249,370 +4249,370 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……仕方ありませんわね。……あと少しだけ付き合ってあげる。</t>
+          <t xml:space="preserve">…………。そうですか。わたくしにも限度というものがありますのよ？</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、もう無理ですわ。お世話になりました……と申し上げたいところですけれど、正直そうも思えませんの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.bold[2]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.ojousama.bold[2]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう決めました。これ以上ここに留まる理由がありません。ごきげんよう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……聞いてくださるの。{record}わたくし、もっと上の舞台を求めておりますの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}決心がつきましたの。わたくし、この団体を去りますわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ふふ。予想通りですわ。{rivalry}ごきげんよう、社長。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……今更。　……もう心は決まっているわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……仕方ありませんわね。……あと少しだけ付き合ってあげる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.ojousama.bold[1]</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr" s="12">
+      <c r="D132" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.ojousama.bold[1]</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr" s="2">
+      <c r="E132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr" s="3">
+      <c r="F132" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">わたくしへの評価は光栄だけれど、
 今の団体を裏切るなどあり得ませんわ</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.ojousama.bold[1]</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr" s="12">
+      <c r="D133" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.ojousama.bold[1]</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr" s="2">
+      <c r="E133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr" s="3">
+      <c r="F133" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ここがわたくしの居場所なの。
 出直していらして</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.ojousama.bold[1]</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr" s="12">
+      <c r="D134" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.ojousama.bold[1]</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr" s="2">
+      <c r="E134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr" s="3">
+      <c r="F134" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">わたくしを引き抜こうと？
 たいした度胸ですわね</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.ojousama.bold[1]</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr" s="12">
+      <c r="D135" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.ojousama.bold[1]</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr" s="2">
+      <c r="E135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr" s="3">
+      <c r="F135" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">認めてさしあげますわ。
 格の違いをお見せ致します</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ねぇ社長、わたくしどものこと、もっと大切に扱ってくださいませ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ねぇ社長、次のメイン、わたくしたちにお任せいただけませんこと？</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ねぇ社長、わたくしどもの給与、改めてお考えいただけませんこと？</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="40" customHeight="1">
-      <c r="A132" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ねぇ社長、わたくしどもの貢献、きちんと評価していただいておりますの？</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="40" customHeight="1">
-      <c r="A133" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">まあ社長、ありがとうございますわ。その一言で十分ですの。</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="40" customHeight="1">
-      <c r="A134" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…そうですの。失礼いたしましたわ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="40" customHeight="1">
-      <c r="A135" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.ojousama.bold[1]</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…まあ、そういうお心遣いですのね。ありがたく頂戴いたしますわ。</t>
-        </is>
-      </c>
-    </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4637,14 +4637,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、社長ありがとうございますわ。期待に応えてみせますわよ。</t>
+          <t xml:space="preserve">ねぇ社長、わたくしどものこと、もっと大切に扱ってくださいませ。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4669,14 +4669,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの。わかりましたわ。</t>
+          <t xml:space="preserve">ねぇ社長、次のメイン、わたくしたちにお任せいただけませんこと？</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4701,14 +4701,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そういうご配慮ですのね。ありがたく頂戴いたしますわ。</t>
+          <t xml:space="preserve">ねぇ社長、わたくしどもの給与、改めてお考えいただけませんこと？</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4733,14 +4733,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ社長、ありがとうございますわ。みんなに伝えますわね。</t>
+          <t xml:space="preserve">ねぇ社長、わたくしどもの貢献、きちんと評価していただいておりますの？</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4765,14 +4765,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの。承知いたしましたわ。</t>
+          <t xml:space="preserve">まあ社長、ありがとうございますわ。その一言で十分ですの。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4797,14 +4797,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そういうお心遣いですのね。ありがたく頂戴いたしますわ。</t>
+          <t xml:space="preserve">…そうですの。失礼いたしましたわ。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4829,14 +4829,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ社長、ありがとうございますわ。励みになりますの。</t>
+          <t xml:space="preserve">…まあ、そういうお心遣いですのね。ありがたく頂戴いたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4861,14 +4861,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの。失礼いたしましたわ。</t>
+          <t xml:space="preserve">まあ、社長ありがとうございますわ。期待に応えてみせますわよ。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4893,14 +4893,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そういうお心遣いですのね。ありがたく頂戴いたしますわ。</t>
+          <t xml:space="preserve">…そうですの。わかりましたわ。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4925,14 +4925,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの、次はお声をかけますわ。</t>
+          <t xml:space="preserve">…まあ、そういうご配慮ですのね。ありがたく頂戴いたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4957,14 +4957,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。仲間内のお付き合いも大事ですものね。</t>
+          <t xml:space="preserve">まあ社長、ありがとうございますわ。みんなに伝えますわね。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -4989,14 +4989,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの、気をつけますわ。</t>
+          <t xml:space="preserve">…そうですの。承知いたしましたわ。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5021,14 +5021,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。</t>
+          <t xml:space="preserve">…まあ、そういうお心遣いですのね。ありがたく頂戴いたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5053,14 +5053,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの、営業に響くなら線を引きますわ。</t>
+          <t xml:space="preserve">まあ社長、ありがとうございますわ。励みになりますの。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5085,14 +5085,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。これも仕事のうちですもの。</t>
+          <t xml:space="preserve">…そうですの。失礼いたしましたわ。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5117,14 +5117,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご迷惑おかけしましたわ。明日から、ちゃんと出ますわ。</t>
+          <t xml:space="preserve">…まあ、そういうお心遣いですのね。ありがたく頂戴いたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5149,14 +5149,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。次はちゃんといたしますわ。</t>
+          <t xml:space="preserve">…そうですの、次はお声をかけますわ。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5181,14 +5181,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そういうご配慮ですのね。ありがたく頂戴いたしますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。仲間内のお付き合いも大事ですものね。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5213,14 +5213,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。少し休ませていただきますわ。</t>
+          <t xml:space="preserve">…そうですの、気をつけますわ。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5245,14 +5245,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫ですわ。問題ございませんわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5277,14 +5277,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、メンバーケアですの。わたくしも楽になりますわ。</t>
+          <t xml:space="preserve">…そうですの、営業に響くなら線を引きますわ。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5309,14 +5309,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの。わたくしから皆に話しますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。これも仕事のうちですもの。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5341,14 +5341,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。穏便にいたしますわ。</t>
+          <t xml:space="preserve">…ご迷惑おかけしましたわ。明日から、ちゃんと出ますわ。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、ご配慮ありがたく頂戴いたしますわ。下の子のフォロー、助かりますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。次はちゃんといたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5405,14 +5405,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですの。気をつけますわ。</t>
+          <t xml:space="preserve">…まあ、そういうご配慮ですのね。ありがたく頂戴いたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5437,14 +5437,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（扇を畳むように、口を閉ざしましたわ）</t>
+          <t xml:space="preserve">…ありがとうございますわ。少し休ませていただきますわ。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5469,14 +5469,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、ご配慮ありがたく頂戴いたしますわ。</t>
+          <t xml:space="preserve">…大丈夫ですわ。問題ございませんわ。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知いたしましたわ。怪我は本末転倒ですものね、緩めますわ。</t>
+          <t xml:space="preserve">…まあ、メンバーケアですの。わたくしも楽になりますわ。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5533,14 +5533,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございますわ。このまま続けますわ。</t>
+          <t xml:space="preserve">…そうですの。わたくしから皆に話しますわ。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5565,14 +5565,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、下の子のケアですのね。ありがたく頂戴いたしますわ。</t>
+          <t xml:space="preserve">…ありがとうございますわ。穏便にいたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.ojousama</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.attack.ojousama</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5597,14 +5597,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう、同じ場所には立てませんわ</t>
+          <t xml:space="preserve">…まあ、ご配慮ありがたく頂戴いたしますわ。下の子のフォロー、助かりますわ。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.ojousama</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.defend.ojousama</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5629,14 +5629,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくてよ。お受けいたしましょう</t>
+          <t xml:space="preserve">…そうですの。気をつけますわ。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5646,29 +5646,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然ね。まだまだこんなものでは無くてよ</t>
+          <t xml:space="preserve">（扇を畳むように、口を閉ざしましたわ）</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5678,29 +5678,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少しでなにかが掴めそうな。……あと一歩ね。</t>
+          <t xml:space="preserve">…まあ、ご配慮ありがたく頂戴いたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5710,29 +5710,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は調子がいいの。手加減は無用ですわね</t>
+          <t xml:space="preserve">…承知いたしましたわ。怪我は本末転倒ですものね、緩めますわ。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5742,29 +5742,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は重いですけれど。…認めるつもりはありません</t>
+          <t xml:space="preserve">…ありがとうございますわ。このまま続けますわ。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.ojousama.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5774,29 +5774,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.ojousama.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ動けます。…少し、体が言うことを聞きませんが</t>
+          <t xml:space="preserve">…まあ、下の子のケアですのね。ありがたく頂戴いたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.ojousama.bold[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.ojousama</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5806,29 +5806,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.ojousama.bold[1]</t>
+          <t xml:space="preserve">bold.attack.ojousama</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この壁だけは…超えられないのかしら</t>
+          <t xml:space="preserve">もう、同じ場所には立てませんわ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.ojousama.bold[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.ojousama</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5838,29 +5838,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.ojousama.bold[1]</t>
+          <t xml:space="preserve">bold.defend.ojousama</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂が見えてきましたわ。手を伸ばせば届く距離に</t>
+          <t xml:space="preserve">よろしくてよ。お受けいたしましょう</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.ojousama.bold[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5885,14 +5885,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここからが本番ですわ。見ていてくださいませ</t>
+          <t xml:space="preserve">当然ね。まだまだこんなものでは無くてよ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.ojousama.bold[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂の景色…悪くありませんわね</t>
+          <t xml:space="preserve">もう少しでなにかが掴めそうな。……あと一歩ね。</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.ojousama.bold[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.ojousama.bold[1]</t>
+          <t xml:space="preserve">fresh.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5949,14 +5949,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この声援に恥じぬ試合をお見せしますわ</t>
+          <t xml:space="preserve">今日は調子がいいの。手加減は無用ですわね</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">heavy.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5981,14 +5981,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…燃えないわね。…何をしても、火がつかないのよ</t>
+          <t xml:space="preserve">体は重いですけれど。…認めるつもりはありません</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">warm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6013,14 +6013,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目が覚めたわ。ここで終わるわけにはいかないもの</t>
+          <t xml:space="preserve">まだ動けます。…少し、体が言うことを聞きませんが</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">cap_reached.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6045,14 +6045,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し待たせたかしら？ここからよ</t>
+          <t xml:space="preserve">この壁だけは…超えられないのかしら</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.ojousama.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6062,12 +6062,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.ojousama.bold[1]</t>
+          <t xml:space="preserve">ovr_elite.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6077,14 +6077,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何をしてるの？私ほどの者が……</t>
+          <t xml:space="preserve">頂が見えてきましたわ。手を伸ばせば届く距離に</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.ojousama.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.ojousama.bold[1]</t>
+          <t xml:space="preserve">ovr_growth.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6109,14 +6109,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう治ったのに…なぜこんなにもたつくの？</t>
+          <t xml:space="preserve">ここからが本番ですわ。見ていてくださいませ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.ojousama.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.ojousama.bold[1]</t>
+          <t xml:space="preserve">ovr_legend.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6141,14 +6141,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしが…怯える？ そんなはずは</t>
+          <t xml:space="preserve">頂の景色…悪くありませんわね</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.ojousama.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.ojousama.bold[1]</t>
+          <t xml:space="preserve">pop_star.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6173,14 +6173,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は万全ですのに…気持ちがついてきませんわね</t>
+          <t xml:space="preserve">この声援に恥じぬ試合をお見せしますわ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.ojousama.bold[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6190,29 +6190,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちの団体が最強だと、証明できましたわね。</t>
+          <t xml:space="preserve">…燃えないわね。…何をしても、火がつかないのよ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.bold[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6222,29 +6222,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方と全力で戦えたことは、大変名誉ですわ</t>
+          <t xml:space="preserve">目が覚めたわ。ここで終わるわけにはいかないもの</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.ojousama.bold[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6254,29 +6254,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この王座はわたくしに最もふさわしい。それを証明し続けますわ</t>
+          <t xml:space="preserve">少し待たせたかしら？ここからよ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6286,29 +6286,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.ojousama.bold[1]</t>
+          <t xml:space="preserve">defeat.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの名が歴史に刻まれる。…ふさわしいと、自分で思えますわ</t>
+          <t xml:space="preserve">…何をしてるの？私ほどの者が……</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6318,29 +6318,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.ojousama.bold[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしが最も輝いた一年でしたわね。異論のある方はリングでお待ちしています</t>
+          <t xml:space="preserve">もう治ったのに…なぜこんなにもたつくの？</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6350,29 +6350,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.ojousama.bold[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ですわね。わたくしの実力を見れば、誰もが納得するでしょう？</t>
+          <t xml:space="preserve">わたくしが…怯える？ そんなはずは</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.ojousama.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6382,29 +6382,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.ojousama.bold[1]</t>
+          <t xml:space="preserve">penalty_end.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちの連係に、並のタッグが届くはずもありませんわ。</t>
+          <t xml:space="preserve">体は万全ですのに…気持ちがついてきませんわね</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">autumnWarChampion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6429,14 +6429,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム。……ようやく、相応しい場所ね</t>
+          <t xml:space="preserve">わたくしたちの団体が最強だと、証明できましたわね。</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">bestMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6461,14 +6461,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほほほ、わたくしの本気、ご覧に入れましょう！</t>
+          <t xml:space="preserve">あの方と全力で戦えたことは、大変名誉ですわ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[3]</t>
+          <t xml:space="preserve">champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6493,14 +6493,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリング、わたくしの独壇場にしてみせますわ！</t>
+          <t xml:space="preserve">この王座はわたくしに最もふさわしい。それを証明し続けますわ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">hallOfFame.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6525,14 +6525,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員……ふふ、当然でしょうね。この顔ぶれですもの</t>
+          <t xml:space="preserve">わたくしの名が歴史に刻まれる。…ふさわしいと、自分で思えますわ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">mvp.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6557,14 +6557,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様方の歓声、まだ耳に焼き付いておりますの！</t>
+          <t xml:space="preserve">わたくしが最も輝いた一年でしたわね。異論のある方はリングでお待ちしています</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[3]</t>
+          <t xml:space="preserve">rookie.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6589,14 +6589,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この勢い、止めてはなりませんわよ！！</t>
+          <t xml:space="preserve">当然の結果ですわね。わたくしの実力を見れば、誰もが納得するでしょう？</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6606,29 +6606,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.ojousama.bold[1]</t>
+          <t xml:space="preserve">springTagChampion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだですわ。もっと上を目指しませんと…</t>
+          <t xml:space="preserve">わたくしたちの連係に、並のタッグが届くはずもありませんわ。</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6638,29 +6638,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様のご期待が、わたくしの力になっておりますわ</t>
+          <t xml:space="preserve">ドーム。……ようやく、相応しい場所ね</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度、問題ありませんわ</t>
+          <t xml:space="preserve">ほほほ、わたくしの本気、ご覧に入れましょう！</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6702,29 +6702,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この声援を力に、さらに上を目指しますわ</t>
+          <t xml:space="preserve">このリング、わたくしの独壇場にしてみせますわ！</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6734,29 +6734,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この団体で、私の夢は叶えられますの…？</t>
+          <t xml:space="preserve">満員……ふふ、当然でしょうね。この顔ぶれですもの</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6766,29 +6766,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままで本当によろしいのか、と考えてしまいますの</t>
+          <t xml:space="preserve">お客様方の歓声、まだ耳に焼き付いておりますの！</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.bold[3]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6798,29 +6798,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[3]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わたくしの価値、ちゃんと見てくださっているのかしら</t>
+          <t xml:space="preserve">この勢い、止めてはなりませんわよ！！</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.ojousama.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.ojousama.bold[1]</t>
+          <t xml:space="preserve">N1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6845,14 +6845,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わたくしにふさわしい舞台がまだ来ないなんて</t>
+          <t xml:space="preserve">まだまだですわ。もっと上を目指しませんと…</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.ojousama.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6862,29 +6862,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.ojousama.bold[1]</t>
+          <t xml:space="preserve">N2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お断りしますわ。わたくしの価値は、この程度ではありませんの</t>
+          <t xml:space="preserve">皆様のご期待が、わたくしの力になっておりますわ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6894,29 +6894,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.ojousama.bold[1]</t>
+          <t xml:space="preserve">N3.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。結果でお返しするわ</t>
+          <t xml:space="preserve">この程度、問題ありませんわ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6926,29 +6926,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.ojousama.bold[1]</t>
+          <t xml:space="preserve">N4.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この合宿で一段上へ参りましょう</t>
+          <t xml:space="preserve">この声援を力に、さらに上を目指しますわ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6958,29 +6958,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.ojousama.bold[1]</t>
+          <t xml:space="preserve">N5_low.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが信じているなら、応えてあげませんとね？</t>
+          <t xml:space="preserve">…この団体で、私の夢は叶えられますの…？</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6990,29 +6990,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.ojousama.bold[1]</t>
+          <t xml:space="preserve">N5_warning.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなところで終わりませんわ！</t>
+          <t xml:space="preserve">…このままで本当によろしいのか、と考えてしまいますの</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.ojousama.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7022,29 +7022,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.ojousama.bold[1]</t>
+          <t xml:space="preserve">G1.voice.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">納得はしておりません。そこだけは、申し上げておきます</t>
+          <t xml:space="preserve">…わたくしの価値、ちゃんと見てくださっているのかしら</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7054,29 +7054,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.ojousama.bold[1]</t>
+          <t xml:space="preserve">G3.voice.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">より広い舞台へということね。当然ね。</t>
+          <t xml:space="preserve">…わたくしにふさわしい舞台がまだ来ないなんて</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.ojousama.bold[1]</t>
+          <t xml:space="preserve">bonus_insult.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7101,14 +7101,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様の頑張りを、誇りに思いますわ</t>
+          <t xml:space="preserve">お断りしますわ。わたくしの価値は、この程度ではありませんの</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.ojousama.bold[1]</t>
+          <t xml:space="preserve">bonus.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7133,14 +7133,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すこし休んでまいりますわ。ごめんあそばせ。</t>
+          <t xml:space="preserve">ありがとうございます。結果でお返しするわ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.ojousama.bold[1]</t>
+          <t xml:space="preserve">camp.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7165,14 +7165,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐ戻ります。待っていなさいな。</t>
+          <t xml:space="preserve">この合宿で一段上へ参りましょう</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.ojousama.bold[1]</t>
+          <t xml:space="preserve">encourage_high_trust.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7197,14 +7197,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この機会、決して無駄にはしない</t>
+          <t xml:space="preserve">あなたが信じているなら、応えてあげませんとね？</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.ojousama.bold[1]</t>
+          <t xml:space="preserve">encourage.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7229,14 +7229,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が出ればお客様も喜ぶでしょうね。楽しみだわ…</t>
+          <t xml:space="preserve">こんなところで終わりませんわ！</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.ojousama.bold[1]</t>
+          <t xml:space="preserve">faction_decree.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7261,14 +7261,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…正直に申しますと、良い条件ですわ</t>
+          <t xml:space="preserve">納得はしておりません。そこだけは、申し上げておきます</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7278,12 +7278,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.ojousama.bold[1]</t>
+          <t xml:space="preserve">media.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7293,14 +7293,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習…？ 出していただけないのに、意味がありますか</t>
+          <t xml:space="preserve">より広い舞台へということね。当然ね。</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.ojousama.bold[2]</t>
+          <t xml:space="preserve">party.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7325,14 +7325,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングに上がれないのなら、稽古など無駄でしょう</t>
+          <t xml:space="preserve">皆様の頑張りを、誇りに思いますわ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.ojousama.bold[1]</t>
+          <t xml:space="preserve">refresh_leave.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7357,14 +7357,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「この扱いの意味、伺いたいものね」と控室で静かに笑ってみせる）</t>
+          <t xml:space="preserve">すこし休んでまいりますわ。ごめんあそばせ。</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.ojousama.bold[1]</t>
+          <t xml:space="preserve">special_treatment.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7389,14 +7389,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「このまま終わるつもりはございません」と宣言めいた投稿）</t>
+          <t xml:space="preserve">すぐ戻ります。待っていなさいな。</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7406,12 +7406,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.ojousama.bold[1]</t>
+          <t xml:space="preserve">trainer.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7421,14 +7421,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンの座、いただきに参りましょう</t>
+          <t xml:space="preserve">この機会、決して無駄にはしない</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.ojousama.bold[1]</t>
+          <t xml:space="preserve">E1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7453,14 +7453,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれとも決着をつけませんとね……</t>
+          <t xml:space="preserve">私が出ればお客様も喜ぶでしょうね。楽しみだわ…</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.ojousama.bold[1]</t>
+          <t xml:space="preserve">E6.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7485,14 +7485,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…情けないけれど、もう、体が限界ですわね</t>
+          <t xml:space="preserve">…正直に申しますと、良い条件ですわ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.ojousama.bold[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7517,14 +7517,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは納得できませんわね。……どうするか、考えなさいね？</t>
+          <t xml:space="preserve">練習…？ 出していただけないのに、意味がありますか</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.ojousama.bold[1]</t>
+          <t xml:space="preserve">S_boycott.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7549,14 +7549,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（膝の上で、手を固く握りしめている）</t>
+          <t xml:space="preserve">リングに上がれないのなら、稽古など無駄でしょう</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.ojousama.bold[1]</t>
+          <t xml:space="preserve">S_grumble.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと上を目指す為に。特訓が必要ね…</t>
+          <t xml:space="preserve">（「この扱いの意味、伺いたいものね」と控室で静かに笑ってみせる）</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.ojousama.bold[1]</t>
+          <t xml:space="preserve">S_sns.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7613,14 +7613,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">若手の面倒を見るのも、私の務めですわね</t>
+          <t xml:space="preserve">（SNSに「このまま終わるつもりはございません」と宣言めいた投稿）</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.ojousama.bold[1]</t>
+          <t xml:space="preserve">S1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7645,14 +7645,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなところで止まるわけにはいかないわ…</t>
+          <t xml:space="preserve">チャンピオンの座、いただきに参りましょう</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.ojousama.bold[1]</t>
+          <t xml:space="preserve">S2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7677,14 +7677,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの女の態度は許せないわね……</t>
+          <t xml:space="preserve">あれとも決着をつけませんとね……</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.ojousama.bold[1]</t>
+          <t xml:space="preserve">S3.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7709,14 +7709,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私も黙ってはいられませんわ。あちらに非があるのだから</t>
+          <t xml:space="preserve">…情けないけれど、もう、体が限界ですわね</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.ojousama.bold[1]</t>
+          <t xml:space="preserve">S4_direct.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7741,14 +7741,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私なら、確かにブランドイメージは上がるでしょうね</t>
+          <t xml:space="preserve">このままでは納得できませんわね。……どうするか、考えなさいね？</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7758,12 +7758,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.ojousama.bold[1]</t>
+          <t xml:space="preserve">S4_silent.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7773,14 +7773,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM？仕方ないわね……品と格というものを知らしめなければ</t>
+          <t xml:space="preserve">…………（膝の上で、手を固く握りしめている）</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.ojousama.bold[1]</t>
+          <t xml:space="preserve">S5.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7805,14 +7805,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方々に最高の時間をお届けしますわ</t>
+          <t xml:space="preserve">もっと上を目指す為に。特訓が必要ね…</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.ojousama.bold[1]</t>
+          <t xml:space="preserve">S6.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7837,14 +7837,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイね……もちろん自信はあるわよ？</t>
+          <t xml:space="preserve">若手の面倒を見るのも、私の務めですわね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.ojousama.bold[1]</t>
+          <t xml:space="preserve">B1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7869,14 +7869,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">撮影？私の魅力を引き出せるのかしら？</t>
+          <t xml:space="preserve">こんなところで止まるわけにはいかないわ…</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.ojousama.bold[1]</t>
+          <t xml:space="preserve">B2_fighter1.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7901,14 +7901,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">トーク番組？妙な仕事を持ってくるものね</t>
+          <t xml:space="preserve">あの女の態度は許せないわね……</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.ojousama.bold[1]</t>
+          <t xml:space="preserve">B2_fighter2.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7933,14 +7933,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、全国の皆様も私の事が気にかかるのかしら？</t>
+          <t xml:space="preserve">私も黙ってはいられませんわ。あちらに非があるのだから</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7950,29 +7950,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">B4_brand.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
+          <t xml:space="preserve">私なら、確かにブランドイメージは上がるでしょうね</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7982,29 +7982,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">B4_cm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">CM？仕方ないわね……品と格というものを知らしめなければ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8014,29 +8014,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">B4_fan.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちますわよ。当然ですの</t>
+          <t xml:space="preserve">ファンの方々に最高の時間をお届けしますわ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8046,29 +8046,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">B4_fashion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">ランウェイね……もちろん自信はあるわよ？</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8078,29 +8078,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">B4_gravure.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
+          <t xml:space="preserve">撮影？私の魅力を引き出せるのかしら？</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8110,29 +8110,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">B4_variety.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
+          <t xml:space="preserve">トーク番組？妙な仕事を持ってくるものね</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8142,29 +8142,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">B4.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を止めるには足りませんわよ</t>
+          <t xml:space="preserve">あらあら、全国の皆様も私の事が気にかかるのかしら？</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8189,14 +8189,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">倒した相手と同じ列に並ばされる屈辱、分かるかしらね？</t>
+          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8221,14 +8221,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">幕を引かれた側の気持ちは、誰も聞きませんのね</t>
+          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8253,14 +8253,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
+          <t xml:space="preserve">頂点に立ちますわよ。当然ですの</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8270,12 +8270,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8285,14 +8285,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.bold[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.bold[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8317,14 +8317,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちますわよ。当然ですの</t>
+          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8349,14 +8349,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い機会をいただいたわ。私を見誤った方々に、答えを見せるとしましょう</t>
+          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8381,14 +8381,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
+          <t xml:space="preserve">私を止めるには足りませんわよ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.ojousama.bold[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8413,14 +8413,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
+          <t xml:space="preserve">倒した相手と同じ列に並ばされる屈辱、分かるかしらね？</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.ojousama.bold[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8445,14 +8445,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は調子がいいの。手加減は無用ですわね</t>
+          <t xml:space="preserve">幕を引かれた側の気持ちは、誰も聞きませんのね</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.ojousama.bold[1]</t>
+          <t xml:space="preserve">draftInterest.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8477,14 +8477,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は重いですけれど。…認めるつもりはありません</t>
+          <t xml:space="preserve">頂点に立つために参りますわ。覚悟はよろしくて？</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.ojousama.bold[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ動けます。…少し、体が言うことを聞きませんが</t>
+          <t xml:space="preserve">チャンピオンになるために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.ojousama.bold[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8541,14 +8541,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
+          <t xml:space="preserve">頂点に立ちますわよ。当然ですの</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.ojousama.bold[2]</t>
+          <t xml:space="preserve">faGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8573,14 +8573,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を止めるには足りませんわよ</t>
+          <t xml:space="preserve">良い機会をいただいたわ。私を見誤った方々に、答えを見せるとしましょう</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.ojousama.bold[1]</t>
+          <t xml:space="preserve">faSigning.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8605,14 +8605,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
+          <t xml:space="preserve">頂点を獲るために参りましたわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.ojousama.bold[2]</t>
+          <t xml:space="preserve">faWelcome.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8637,14 +8637,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで終わりではありませんわよ</t>
+          <t xml:space="preserve">頂点を目指しますわ。ご期待くださいませ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.ojousama.bold[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8669,14 +8669,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
+          <t xml:space="preserve">今日は調子がいいの。手加減は無用ですわね</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.ojousama.bold[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8701,14 +8701,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、お目が高いわね。わたくしに気づくなんて</t>
+          <t xml:space="preserve">体は重いですけれど。…認めるつもりはありません</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.ojousama.bold[1]</t>
+          <t xml:space="preserve">heatSelf.warm.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8733,14 +8733,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これで終わりかしら。もう一度、場を用意していただける？</t>
+          <t xml:space="preserve">まだ動けます。…少し、体が言うことを聞きませんが</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.ojousama.bold[1]</t>
+          <t xml:space="preserve">injury.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8765,14 +8765,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもお譲りしませんわ。もっと上を目指しますの</t>
+          <t xml:space="preserve">このくらい何でもありませんわ。すぐ戻りますの</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.ojousama.bold[1]</t>
+          <t xml:space="preserve">injury.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8797,14 +8797,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めませんわ…！必ず取り返しますの！</t>
+          <t xml:space="preserve">私を止めるには足りませんわよ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.ojousama.bold[1]</t>
+          <t xml:space="preserve">release.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8829,14 +8829,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点に立ちましたわ。でもここからが本当の闘いですの</t>
+          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">release.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8861,14 +8861,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
+          <t xml:space="preserve">これで終わりではありませんわよ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8893,14 +8893,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで終わりではありませんわよ</t>
+          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8910,12 +8910,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">scoutGreeting.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8925,14 +8925,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
+          <t xml:space="preserve">あら、お目が高いわね。わたくしに気づくなんて</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8942,12 +8942,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8964,7 +8964,7 @@
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">titleDefense.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8996,7 +8996,7 @@
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">titleLoss.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9028,7 +9028,7 @@
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">titleWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9060,7 +9060,7 @@
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9070,29 +9070,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合いません。どうしても</t>
+          <t xml:space="preserve">悔しいですが…次の場所で必ず証明いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9102,29 +9102,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これ以上は望めません。それだけのこと</t>
+          <t xml:space="preserve">これで終わりではありませんわよ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9134,29 +9134,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">壁を作られている気がします。愉快ではありませんね</t>
+          <t xml:space="preserve">レンタルでも手は抜きませんわよ！</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9166,29 +9166,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">以前はもっと言葉を交わしていたはず。…何なのかしら</t>
+          <t xml:space="preserve">……これで終わりかしら。もう一度、場を用意していただける？</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9198,29 +9198,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良き仲間になれそうですわ。認めてあげます</t>
+          <t xml:space="preserve">まだ誰にもお譲りしませんわ。もっと上を目指しますの</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9230,29 +9230,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたち、最強のペアですわ</t>
+          <t xml:space="preserve">認めませんわ…！必ず取り返しますの！</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9262,29 +9262,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、済んだこと</t>
+          <t xml:space="preserve">頂点に立ちましたわ。でもここからが本当の闘いですの</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.ojousama[2]</t>
+          <t xml:space="preserve">bond_39_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9309,14 +9309,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着はつきました。次へ参ります</t>
+          <t xml:space="preserve">合いません。どうしても</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9341,14 +9341,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">打ち負かすこと、楽しみにしておりますわ</t>
+          <t xml:space="preserve">これ以上は望めません。それだけのこと</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9373,14 +9373,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">打ち破ることが、わたくしの使命ですわ</t>
+          <t xml:space="preserve">壁を作られている気がします。愉快ではありませんね</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9405,14 +9405,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方がいたから強くなれました。感謝を…けれど負けません</t>
+          <t xml:space="preserve">以前はもっと言葉を交わしていたはず。…何なのかしら</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.ojousama[2]</t>
+          <t xml:space="preserve">bond_60_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9437,14 +9437,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この戦いは生涯続きます。望むところ</t>
+          <t xml:space="preserve">良き仲間になれそうですわ。認めてあげます</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.ojousama[1]</t>
+          <t xml:space="preserve">bond_80_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9469,14 +9469,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の看板、わたくしが背負って差し上げますわ</t>
+          <t xml:space="preserve">わたくしたち、最強のペアですわ</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9501,14 +9501,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけないでいただきたい。価値が分からぬなら、もう付き合いきれません</t>
+          <t xml:space="preserve">……もう、済んだこと</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9533,14 +9533,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱いは許せません。しかと覚えておくことです</t>
+          <t xml:space="preserve">決着はつきました。次へ参ります</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9565,14 +9565,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの価値をご理解いただけていませんわね</t>
+          <t xml:space="preserve">打ち負かすこと、楽しみにしておりますわ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.ojousama.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.ojousama.bold[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9597,14 +9597,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの出番がないとは…運営の怠慢ですわ</t>
+          <t xml:space="preserve">打ち破ることが、わたくしの使命ですわ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9629,14 +9629,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの感覚は抜けてしまった？でも、得るものは十分でしたわ</t>
+          <t xml:space="preserve">あの方がいたから強くなれました。感謝を…けれど負けません</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9646,29 +9646,29 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.bold[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷の一つや二つ、どうということはありませんわ。最後まで、頂は渡しませんの</t>
+          <t xml:space="preserve">この戦いは生涯続きます。望むところ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9678,29 +9678,29 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.bold[2]</t>
+          <t xml:space="preserve">trust_above_75.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで勝ち残ったのはわたくしですわ。締めくくりも、当然わたくしが</t>
+          <t xml:space="preserve">この団体の看板、わたくしが背負って差し上げますわ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9710,29 +9710,29 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.bold[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと殊勝なこと。ですが、わたくしを越えるのは無理ですわ</t>
+          <t xml:space="preserve">ふざけないでいただきたい。価値が分からぬなら、もう付き合いきれません</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9742,29 +9742,29 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.bold[2]</t>
+          <t xml:space="preserve">trust_below_20.bold.ojousama[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どなたがお相手でも、このリングの主はわたくしですのよ</t>
+          <t xml:space="preserve">この扱いは許せません。しかと覚えておくことです</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9774,29 +9774,29 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.bold[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.ojousama[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、片づけましたわ。…息は乱れていますけれど、まだまだですのよ。次はどなた？</t>
+          <t xml:space="preserve">わたくしの価値をご理解いただけていませんわね</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9806,29 +9806,29 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.bold[2]</t>
+          <t xml:space="preserve">GL-06.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリングの主は、まだわたくしですわ。次の方、覚悟していらして</t>
+          <t xml:space="preserve">わたくしの出番がないとは…運営の怠慢ですわ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9838,29 +9838,29 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この三人が最強でしたわ。他に何か語る必要がありまして？</t>
+          <t xml:space="preserve">あの感覚は抜けてしまった？でも、得るものは十分でしたわ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9870,12 +9870,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.bold[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9885,14 +9885,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたち三人の前に、立てる団体はございませんでしたわね</t>
+          <t xml:space="preserve">傷の一つや二つ、どうということはありませんわ。最後まで、頂は渡しませんの</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.bold[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9917,14 +9917,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はいただきますわ。ですが……次は優勝旗もわたくしの手元に参りますのよ</t>
+          <t xml:space="preserve">ここまで勝ち残ったのはわたくしですわ。締めくくりも、当然わたくしが</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.bold[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9949,14 +9949,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしを甘く見ないでくださいまし。次は、全てを奪い返しますわ</t>
+          <t xml:space="preserve">次から次へと殊勝なこと。ですが、わたくしを越えるのは無理ですわ</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9966,12 +9966,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.bold[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -9981,14 +9981,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人お相手しようと、わたくしを倒せなかった事実は変わりませんわ</t>
+          <t xml:space="preserve">どなたがお相手でも、このリングの主はわたくしですのよ</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -9998,12 +9998,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.bold[2]</t>
+          <t xml:space="preserve">survivor.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10013,14 +10013,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと……けれど、このリングの主はわたくしでしたのよ</t>
+          <t xml:space="preserve">一人、片づけましたわ。…息は乱れていますけれど、まだまだですのよ。次はどなた？</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.bold[1]</t>
+          <t xml:space="preserve">survivor.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10045,14 +10045,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝はわたくしのもの。当然の結果ですわね</t>
+          <t xml:space="preserve">このリングの主は、まだわたくしですわ。次の方、覚悟していらして</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.bold[2]</t>
+          <t xml:space="preserve">champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10077,14 +10077,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これがわたくしの実力。誰もかれもわかったかしら？</t>
+          <t xml:space="preserve">この三人が最強でしたわ。他に何か語る必要がありまして？</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.ojousama.bold[1]</t>
+          <t xml:space="preserve">champion.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10109,14 +10109,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これが結果？ ……信じられないわね</t>
+          <t xml:space="preserve">わたくしたち三人の前に、立てる団体はございませんでしたわね</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.ojousama.bold[2]</t>
+          <t xml:space="preserve">defiant.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10141,14 +10141,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしともあろうものが…屈辱ですわ</t>
+          <t xml:space="preserve">賞はいただきますわ。ですが……次は優勝旗もわたくしの手元に参りますのよ</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.ojousama.bold[1]</t>
+          <t xml:space="preserve">defiant.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10173,14 +10173,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ね</t>
+          <t xml:space="preserve">わたくしを甘く見ないでくださいまし。次は、全てを奪い返しますわ</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.ojousama.bold[2]</t>
+          <t xml:space="preserve">gauntlet.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10205,14 +10205,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度のことで驚いていては、私についてはこられなくてよ？</t>
+          <t xml:space="preserve">何人お相手しようと、わたくしを倒せなかった事実は変わりませんわ</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.ojousama.bold[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10237,14 +10237,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私がこの程度で喜ぶとでも？…次こそ頂点を取りますわ</t>
+          <t xml:space="preserve">次から次へと……けれど、このリングの主はわたくしでしたのよ</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.ojousama.bold[2]</t>
+          <t xml:space="preserve">champion.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10269,14 +10269,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしなら、この程度当然よ</t>
+          <t xml:space="preserve">優勝はわたくしのもの。当然の結果ですわね</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.bold[1]</t>
+          <t xml:space="preserve">champion.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10301,14 +10301,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝は当然の舞台。このまま優勝もいただきましょう</t>
+          <t xml:space="preserve">これがわたくしの実力。誰もかれもわかったかしら？</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.bold[2]</t>
+          <t xml:space="preserve">postLose.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10333,14 +10333,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたで最後ね。……覚悟はできているのかしら</t>
+          <t xml:space="preserve">……これが結果？ ……信じられないわね</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.bold[1]</t>
+          <t xml:space="preserve">postLose.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10365,14 +10365,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝つのは私。それ以外ありえないでしょう？</t>
+          <t xml:space="preserve">わたくしともあろうものが…屈辱ですわ</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.bold[2]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10397,14 +10397,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">格の違いを教えてあげる</t>
+          <t xml:space="preserve">当然の結果ね</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.ojousama.bold[1]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10429,14 +10429,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の選出は、当然ね</t>
+          <t xml:space="preserve">この程度のことで驚いていては、私についてはこられなくてよ？</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.ojousama.bold[2]</t>
+          <t xml:space="preserve">postWin.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10461,14 +10461,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選ばれた以上、出場いたしますわ</t>
+          <t xml:space="preserve">私がこの程度で喜ぶとでも？…次こそ頂点を取りますわ</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10478,12 +10478,12 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">postWin.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10493,14 +10493,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">容赦は出来ないわ。覚悟する事ね</t>
+          <t xml:space="preserve">わたくしなら、この程度当然よ</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10525,14 +10525,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この座は渡せませんわね…… ずっと目指してきましたのよ……！</t>
+          <t xml:space="preserve">決勝は当然の舞台。このまま優勝もいただきましょう</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10542,12 +10542,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10557,14 +10557,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そちらの団体のレベル、存じておりますわよ？</t>
+          <t xml:space="preserve">あなたで最後ね。……覚悟はできているのかしら</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10574,12 +10574,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10589,14 +10589,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">格の違いをお教えして差し上げますわ</t>
+          <t xml:space="preserve">勝つのは私。それ以外ありえないでしょう？</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10606,12 +10606,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10621,14 +10621,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらまあ。逃げ足が速い…格の違いは理解出来たみたいね</t>
+          <t xml:space="preserve">格の違いを教えてあげる</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10638,12 +10638,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">summon.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10653,14 +10653,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ……みっともないこと。</t>
+          <t xml:space="preserve">私の選出は、当然ね</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.ojousama.bold[1]</t>
+          <t xml:space="preserve">summon.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10685,14 +10685,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘…こんな結果…認めませんわ…！</t>
+          <t xml:space="preserve">選ばれた以上、出場いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.bold[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10702,12 +10702,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.ojousama.bold[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10717,14 +10717,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次こそは…必ず…覚悟なさい！</t>
+          <t xml:space="preserve">容赦は出来ないわ。覚悟する事ね</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.bold[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10749,14 +10749,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ですわ。格の違い、おわかりになりまして？</t>
+          <t xml:space="preserve">この座は渡せませんわね…… ずっと目指してきましたのよ……！</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.bold[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.ojousama.bold[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10781,14 +10781,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">圧勝ですわね。ふふっ</t>
+          <t xml:space="preserve">そちらの団体のレベル、存じておりますわよ？</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10813,14 +10813,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ね。……私を甘く見るべきではなかったわね</t>
+          <t xml:space="preserve">格の違いをお教えして差し上げますわ</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[2]</t>
+          <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10845,14 +10845,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で終わりではなくてよ</t>
+          <t xml:space="preserve">あらまあ。逃げ足が速い…格の違いは理解出来たみたいね</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[3]</t>
+          <t xml:space="preserve">ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10877,14 +10877,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の団体に挑むなど……百年早いですわね</t>
+          <t xml:space="preserve">うふふ……みっともないこと。</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10894,29 +10894,29 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.bold[1]</t>
+          <t xml:space="preserve">result_lose.ojousama.bold[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これが頂点の景色……？ ……ふふ、まだ先があるでしょうね</t>
+          <t xml:space="preserve">嘘…こんな結果…認めませんわ…！</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.ojousama.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10926,59 +10926,283 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.bold[1]</t>
+          <t xml:space="preserve">result_lose.ojousama.bold[2]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い機会をいただいたわ。私を見誤った方々に、答えを見せるとしましょう</t>
+          <t xml:space="preserve">次こそは…必ず…覚悟なさい！</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">当然の結果ですわ。格の違い、おわかりになりまして？</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="40" customHeight="1">
+      <c r="A335" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.bold[2]</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.ojousama.bold[2]</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">圧勝ですわね。ふふっ</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="40" customHeight="1">
+      <c r="A336" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">当然の結果ね。……私を甘く見るべきではなかったわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="40" customHeight="1">
+      <c r="A337" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[2]</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.bold[2]</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この程度で終わりではなくてよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="40" customHeight="1">
+      <c r="A338" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.bold[3]</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.bold[3]</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私の団体に挑むなど……百年早いですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="40" customHeight="1">
+      <c r="A339" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">これが頂点の景色……？ ……ふふ、まだ先があるでしょうね</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="40" customHeight="1">
+      <c r="A340" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.bold[1]</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">良い機会をいただいたわ。私を見誤った方々に、答えを見せるとしましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="40" customHeight="1">
+      <c r="A341" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.ojousama.bold[1]</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr" s="2">
+      <c r="B341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr" s="12">
+      <c r="D341" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">ojousama.bold[1]</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr" s="2">
+      <c r="E341" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr" s="3">
+      <c r="F341" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あら、お目が高いわね。わたくしに気づくなんて</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H334"/>
+  <autoFilter ref="A1:H341"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×強気.xlsx
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あの方はわたくしが引き受けますわね。</t>
+          <t xml:space="preserve">社長、あの団体はわたくしたち三人で引き受けますわ。</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方と対戦したいのです。適任はわたくしでしょう。</t>
+          <t xml:space="preserve">あの団体へ三人で挑みたいのです。適任はわたくしでしょう。</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">名指しさせていただくわ。あの相手との舞台、整えられる？</t>
+          <t xml:space="preserve">名指しさせていただくわ。あの団体との三連戦、整えられる？</t>
         </is>
       </c>
     </row>
